--- a/packages/calculators/src/modules/test/4.7-other-livestock-manure/4.7-other-livestock-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.7-other-livestock-manure/4.7-other-livestock-manure.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/4.7-other-livestock-manure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456E6BE9-C8F6-484B-AE45-13CCB9F1ED40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E86353-5B81-F642-99C6-87961E66214A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51220" yWindow="-3180" windowWidth="28800" windowHeight="25760" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="14540" yWindow="2720" windowWidth="28800" windowHeight="25760" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="4.7.1.1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="110">
   <si>
     <t>Livestock type</t>
   </si>
@@ -66,12 +66,6 @@
   </si>
   <si>
     <t>Wethers</t>
-  </si>
-  <si>
-    <t>Maiden breeding</t>
-  </si>
-  <si>
-    <t>does/nannies</t>
   </si>
   <si>
     <t>Breeding does/nannies</t>
@@ -462,6 +456,9 @@
   <si>
     <t>Mleach</t>
   </si>
+  <si>
+    <t>Maiden breeding does/nannies</t>
+  </si>
 </sst>
 </file>
 
@@ -544,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -562,7 +559,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -945,18 +941,18 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="AA3" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AM3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN3">
         <v>0.21</v>
       </c>
       <c r="AP3" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AQ3">
         <v>0.24</v>
@@ -1018,20 +1014,20 @@
         <v>1779</v>
       </c>
       <c r="AA4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AG4">
         <v>1753</v>
       </c>
       <c r="AM4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN4">
         <f>44/28</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="AP4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AQ4">
         <v>1.0999999999999999E-2</v>
@@ -1039,67 +1035,67 @@
     </row>
     <row r="5" spans="1:45">
       <c r="C5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="S5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="U5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="W5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="X5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Z5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AG5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AM5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AN5">
         <v>0.6784</v>
       </c>
       <c r="AP5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AQ5">
         <v>0.19</v>
@@ -1109,10 +1105,10 @@
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="AL6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AN6">
         <v>6.0000000000000001E-3</v>
@@ -1120,7 +1116,7 @@
     </row>
     <row r="7" spans="1:45">
       <c r="AM7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN7">
         <v>2E-3</v>
@@ -1135,15 +1131,15 @@
     <row r="9" spans="1:45">
       <c r="A9" s="4"/>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AN9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP9" s="2"/>
       <c r="AQ9" s="2"/>
       <c r="AS9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="17">
@@ -1157,118 +1153,117 @@
         <v>2</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
         <v>33</v>
       </c>
-      <c r="H10" t="s">
+      <c r="K10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N10" t="s">
+        <v>53</v>
+      </c>
+      <c r="O10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q10" t="s">
         <v>43</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="11" t="s">
+      <c r="R10" t="s">
+        <v>45</v>
+      </c>
+      <c r="S10" t="s">
+        <v>87</v>
+      </c>
+      <c r="T10" t="s">
+        <v>47</v>
+      </c>
+      <c r="U10" t="s">
+        <v>48</v>
+      </c>
+      <c r="V10" t="s">
+        <v>37</v>
+      </c>
+      <c r="W10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X10" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z10" t="s">
         <v>61</v>
       </c>
-      <c r="L10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="R10" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="S10" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="T10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="U10" s="11" t="s">
+      <c r="AA10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD10" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="V10" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="W10" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="X10" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y10" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z10" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA10" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB10" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC10" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD10" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE10" s="11" t="s">
-        <v>95</v>
+      <c r="AE10" t="s">
+        <v>93</v>
       </c>
       <c r="AF10" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG10" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH10" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ10" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="AH10" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="AI10" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="AJ10" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="AK10" s="11"/>
       <c r="AM10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AN10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AO10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP10" s="2"/>
       <c r="AQ10" s="2"/>
       <c r="AR10" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AS10" s="2">
         <v>5.8999999999999999E-3</v>
@@ -1285,31 +1280,31 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H11" t="str">
         <f>VLOOKUP(G11,$AR$31:$AS$40,2,FALSE)</f>
         <v>wet</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J11">
         <f>VLOOKUP(A11, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K11">
-        <f>$AQ$5</f>
+        <f t="shared" ref="K11:K30" si="0">$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M11">
         <f>1-N11</f>
@@ -1320,7 +1315,7 @@
         <v>1</v>
       </c>
       <c r="O11">
-        <f>$AN$4</f>
+        <f t="shared" ref="O11:O30" si="1">$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P11">
@@ -1340,15 +1335,15 @@
         <v>0.21</v>
       </c>
       <c r="T11">
-        <f>$AQ$3</f>
+        <f t="shared" ref="T11:T30" si="2">$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U11">
-        <f>$AQ$4</f>
+        <f t="shared" ref="U11:U30" si="3">$AQ$4</f>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V11">
-        <f>$AN$5</f>
+        <f t="shared" ref="V11:V30" si="4">$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W11">
@@ -1364,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>$AM$33</f>
+        <f t="shared" ref="Z11:Z30" si="5">$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA11">
@@ -1383,7 +1378,7 @@
         <f>(AB11+AC11)*10^-3</f>
         <v>3.0183028512000003E-3</v>
       </c>
-      <c r="AE11" s="11">
+      <c r="AE11">
         <f>C11*P11*365</f>
         <v>72087.5</v>
       </c>
@@ -1419,7 +1414,7 @@
       <c r="AP11" s="2"/>
       <c r="AQ11" s="2"/>
       <c r="AR11" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AS11" s="2">
         <v>7.0000000000000001E-3</v>
@@ -1436,31 +1431,31 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" ref="H12:H30" si="0">VLOOKUP(G12,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" ref="H12:H30" si="6">VLOOKUP(G12,$AR$31:$AS$40,2,FALSE)</f>
         <v>wet</v>
       </c>
       <c r="I12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J12">
         <f>VLOOKUP(A12, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K12">
-        <f>$AQ$5</f>
+        <f t="shared" si="0"/>
         <v>0.19</v>
       </c>
       <c r="L12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M12">
         <f>1-N12</f>
@@ -1471,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="O12">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P12">
@@ -1487,23 +1482,23 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <f t="shared" ref="S12:S30" si="1">$AN$3</f>
+        <f t="shared" ref="S12:S30" si="7">$AN$3</f>
         <v>0.21</v>
       </c>
       <c r="T12">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U12">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V12">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W12">
-        <f t="shared" ref="W12:W30" si="2">IF(H12="wet",$AN$6,$AN$7)</f>
+        <f t="shared" ref="W12:W30" si="8">IF(H12="wet",$AN$6,$AN$7)</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X12">
@@ -1515,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA12">
@@ -1534,32 +1529,32 @@
         <f>(AB12+AC12)*10^-3</f>
         <v>3.6219634214400007E-3</v>
       </c>
-      <c r="AE12" s="11">
-        <f t="shared" ref="AE12:AE30" si="3">C12*P12*365</f>
+      <c r="AE12">
+        <f t="shared" ref="AE12:AE30" si="9">C12*P12*365</f>
         <v>86505</v>
       </c>
       <c r="AF12">
-        <f t="shared" ref="AF12:AF30" si="4">AE12*W12*O12*10^-3</f>
+        <f t="shared" ref="AF12:AF30" si="10">AE12*W12*O12*10^-3</f>
         <v>0.81561857142857142</v>
       </c>
       <c r="AG12">
-        <f t="shared" ref="AG12:AG30" si="5">AE12*S12</f>
+        <f t="shared" ref="AG12:AG30" si="11">AE12*S12</f>
         <v>18166.05</v>
       </c>
       <c r="AH12">
-        <f t="shared" ref="AH12:AH30" si="6">AG12*Q12*O12*10^-3</f>
+        <f t="shared" ref="AH12:AH30" si="12">AG12*Q12*O12*10^-3</f>
         <v>0.19982654999999999</v>
       </c>
       <c r="AI12">
-        <f t="shared" ref="AI12:AI30" si="7">AE12*R12*T12</f>
+        <f t="shared" ref="AI12:AI30" si="13">AE12*R12*T12</f>
         <v>0</v>
       </c>
       <c r="AJ12">
-        <f t="shared" ref="AJ12:AJ30" si="8">AI12*U12*O12*10^-3</f>
+        <f t="shared" ref="AJ12:AJ30" si="14">AI12*U12*O12*10^-3</f>
         <v>0</v>
       </c>
       <c r="AM12" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AN12" s="2">
         <v>0.34</v>
@@ -1570,7 +1565,7 @@
       <c r="AP12" s="2"/>
       <c r="AQ12" s="2"/>
       <c r="AR12" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AS12" s="2">
         <v>1.8E-3</v>
@@ -1587,130 +1582,130 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H13" t="str">
+        <f t="shared" si="6"/>
+        <v>wet</v>
+      </c>
+      <c r="I13" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13">
+        <f t="shared" ref="J13:J30" si="15">VLOOKUP(A13, $AM$11:$AN$18,2,FALSE)</f>
+        <v>2.73</v>
+      </c>
+      <c r="K13">
         <f t="shared" si="0"/>
-        <v>wet</v>
-      </c>
-      <c r="I13" t="s">
-        <v>67</v>
-      </c>
-      <c r="J13">
-        <f t="shared" ref="J13:J30" si="9">VLOOKUP(A13, $AM$11:$AN$18,2,FALSE)</f>
-        <v>2.73</v>
-      </c>
-      <c r="K13">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M13">
-        <f t="shared" ref="M13:M30" si="10">1-N13</f>
+        <f t="shared" ref="M13:M30" si="16">1-N13</f>
         <v>0</v>
       </c>
       <c r="N13">
-        <f t="shared" ref="N13:N30" si="11">IF(L13="yes", 1, 0.95)</f>
+        <f t="shared" ref="N13:N30" si="17">IF(L13="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O13">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P13">
-        <f t="shared" ref="P13:P30" si="12">VLOOKUP(A13, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" ref="P13:P30" si="18">VLOOKUP(A13, $AM$11:$AO$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q13">
-        <f t="shared" ref="Q13:Q30" si="13">VLOOKUP(E13,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" ref="Q13:Q30" si="19">VLOOKUP(E13,$AR$10:$AS$22,2,FALSE)</f>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R13:R30" si="14">IF(D13="yes", 1, 0)</f>
+        <f t="shared" ref="R13:R30" si="20">IF(D13="yes", 1, 0)</f>
         <v>1</v>
       </c>
       <c r="S13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T13">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U13">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V13">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X13">
-        <f t="shared" ref="X13:X30" si="15">VLOOKUP(I13,$AM$23:$AN$30,2,FALSE)</f>
+        <f t="shared" ref="X13:X30" si="21">VLOOKUP(I13,$AM$23:$AN$30,2,FALSE)</f>
         <v>0.78</v>
       </c>
       <c r="Y13">
-        <f t="shared" ref="Y13:Y30" si="16">J13*K13*M13*X13*V13</f>
+        <f t="shared" ref="Y13:Y30" si="22">J13*K13*M13*X13*V13</f>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA13">
-        <f t="shared" ref="AA13:AA30" si="17">J13*K13*N13*Z13*V13</f>
+        <f t="shared" ref="AA13:AA30" si="23">J13*K13*N13*Z13*V13</f>
         <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB13">
-        <f t="shared" ref="AB13:AB30" si="18">C13*Y13*365</f>
+        <f t="shared" ref="AB13:AB30" si="24">C13*Y13*365</f>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f t="shared" ref="AC13:AC30" si="19">C13*AA13*365</f>
+        <f t="shared" ref="AC13:AC30" si="25">C13*AA13*365</f>
         <v>4.22562399168</v>
       </c>
       <c r="AD13">
-        <f t="shared" ref="AD13:AD30" si="20">(AB13+AC13)*10^-3</f>
+        <f t="shared" ref="AD13:AD30" si="26">(AB13+AC13)*10^-3</f>
         <v>4.2256239916799998E-3</v>
       </c>
-      <c r="AE13" s="11">
-        <f t="shared" si="3"/>
+      <c r="AE13">
+        <f t="shared" si="9"/>
         <v>100922.5</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0.95155499999999993</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>21193.724999999999</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.19649610749999999</v>
       </c>
       <c r="AI13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>24221.399999999998</v>
       </c>
       <c r="AJ13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.41868419999999995</v>
       </c>
       <c r="AM13" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AN13" s="2">
         <v>0.91</v>
@@ -1721,7 +1716,7 @@
       <c r="AP13" s="2"/>
       <c r="AQ13" s="2"/>
       <c r="AR13" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AS13" s="2">
         <v>2.8999999999999998E-3</v>
@@ -1738,130 +1733,130 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H14" t="str">
+        <f t="shared" si="6"/>
+        <v>wet</v>
+      </c>
+      <c r="I14" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="15"/>
+        <v>2.73</v>
+      </c>
+      <c r="K14">
         <f t="shared" si="0"/>
-        <v>wet</v>
-      </c>
-      <c r="I14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J14">
+        <v>0.19</v>
+      </c>
+      <c r="L14" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="1"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="18"/>
+        <v>39.5</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="19"/>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="7"/>
+        <v>0.21</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="2"/>
+        <v>0.24</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="3"/>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="4"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="8"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X14">
+        <f t="shared" si="21"/>
+        <v>0.78</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="5"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="23"/>
+        <v>1.6538645760000002E-3</v>
+      </c>
+      <c r="AB14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="25"/>
+        <v>4.8292845619200007</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="26"/>
+        <v>4.8292845619200006E-3</v>
+      </c>
+      <c r="AE14">
         <f t="shared" si="9"/>
-        <v>2.73</v>
-      </c>
-      <c r="K14">
-        <f>$AQ$5</f>
-        <v>0.19</v>
-      </c>
-      <c r="L14" t="s">
-        <v>57</v>
-      </c>
-      <c r="M14">
+        <v>115340</v>
+      </c>
+      <c r="AF14">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="N14">
+        <v>1.0874914285714286</v>
+      </c>
+      <c r="AG14">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <f>$AN$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P14">
+        <v>24221.399999999998</v>
+      </c>
+      <c r="AH14">
         <f t="shared" si="12"/>
-        <v>39.5</v>
-      </c>
-      <c r="Q14">
+        <v>0.26643539999999999</v>
+      </c>
+      <c r="AI14">
         <f t="shared" si="13"/>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S14">
-        <f t="shared" si="1"/>
-        <v>0.21</v>
-      </c>
-      <c r="T14">
-        <f>$AQ$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U14">
-        <f>$AQ$4</f>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V14">
-        <f>$AN$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W14">
-        <f t="shared" si="2"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X14">
-        <f t="shared" si="15"/>
-        <v>0.78</v>
-      </c>
-      <c r="Y14">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <f>$AM$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA14">
-        <f t="shared" si="17"/>
-        <v>1.6538645760000002E-3</v>
-      </c>
-      <c r="AB14">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <f t="shared" si="19"/>
-        <v>4.8292845619200007</v>
-      </c>
-      <c r="AD14">
-        <f t="shared" si="20"/>
-        <v>4.8292845619200006E-3</v>
-      </c>
-      <c r="AE14" s="11">
-        <f t="shared" si="3"/>
-        <v>115340</v>
-      </c>
-      <c r="AF14">
-        <f t="shared" si="4"/>
-        <v>1.0874914285714286</v>
-      </c>
-      <c r="AG14">
-        <f t="shared" si="5"/>
-        <v>24221.399999999998</v>
-      </c>
-      <c r="AH14">
-        <f t="shared" si="6"/>
-        <v>0.26643539999999999</v>
-      </c>
-      <c r="AI14">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
       <c r="AM14" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AN14" s="2">
         <v>2.73</v>
@@ -1872,7 +1867,7 @@
       <c r="AP14" s="2"/>
       <c r="AQ14" s="2"/>
       <c r="AR14" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AS14" s="2">
         <v>8.0000000000000002E-3</v>
@@ -1880,7 +1875,7 @@
     </row>
     <row r="15" spans="1:45" ht="17">
       <c r="A15" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
@@ -1889,130 +1884,130 @@
         <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H15" t="str">
+        <f t="shared" si="6"/>
+        <v>wet</v>
+      </c>
+      <c r="I15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="15"/>
+        <v>0.34</v>
+      </c>
+      <c r="K15">
         <f t="shared" si="0"/>
-        <v>wet</v>
-      </c>
-      <c r="I15" t="s">
-        <v>67</v>
-      </c>
-      <c r="J15">
+        <v>0.19</v>
+      </c>
+      <c r="L15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="1"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="18"/>
+        <v>7</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="19"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="7"/>
+        <v>0.21</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="2"/>
+        <v>0.24</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="3"/>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="4"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="8"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="21"/>
+        <v>0.78</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="5"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="23"/>
+        <v>2.0597580800000003E-4</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="25"/>
+        <v>0.67663052928000011</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="26"/>
+        <v>6.7663052928000015E-4</v>
+      </c>
+      <c r="AE15">
         <f t="shared" si="9"/>
-        <v>0.34</v>
-      </c>
-      <c r="K15">
-        <f>$AQ$5</f>
-        <v>0.19</v>
-      </c>
-      <c r="L15" t="s">
-        <v>57</v>
-      </c>
-      <c r="M15">
+        <v>22995</v>
+      </c>
+      <c r="AF15">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="N15">
+        <v>0.21681</v>
+      </c>
+      <c r="AG15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <f>$AN$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P15">
+        <v>4828.95</v>
+      </c>
+      <c r="AH15">
         <f t="shared" si="12"/>
-        <v>7</v>
-      </c>
-      <c r="Q15">
+        <v>1.3659029999999999E-2</v>
+      </c>
+      <c r="AI15">
         <f t="shared" si="13"/>
-        <v>1.8E-3</v>
-      </c>
-      <c r="R15">
+        <v>5518.8</v>
+      </c>
+      <c r="AJ15">
         <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="1"/>
-        <v>0.21</v>
-      </c>
-      <c r="T15">
-        <f>$AQ$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U15">
-        <f>$AQ$4</f>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V15">
-        <f>$AN$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="2"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="15"/>
-        <v>0.78</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <f>$AM$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA15">
-        <f t="shared" si="17"/>
-        <v>2.0597580800000003E-4</v>
-      </c>
-      <c r="AB15">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" si="19"/>
-        <v>0.67663052928000011</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" si="20"/>
-        <v>6.7663052928000015E-4</v>
-      </c>
-      <c r="AE15" s="11">
-        <f t="shared" si="3"/>
-        <v>22995</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="4"/>
-        <v>0.21681</v>
-      </c>
-      <c r="AG15">
-        <f t="shared" si="5"/>
-        <v>4828.95</v>
-      </c>
-      <c r="AH15">
-        <f t="shared" si="6"/>
-        <v>1.3659029999999999E-2</v>
-      </c>
-      <c r="AI15">
-        <f t="shared" si="7"/>
-        <v>5518.8</v>
-      </c>
-      <c r="AJ15">
-        <f t="shared" si="8"/>
         <v>9.5396400000000006E-2</v>
       </c>
       <c r="AM15" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AN15" s="2">
         <v>0.34</v>
@@ -2023,7 +2018,7 @@
       <c r="AP15" s="2"/>
       <c r="AQ15" s="2"/>
       <c r="AR15" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AS15" s="2">
         <v>1.9900000000000001E-2</v>
@@ -2031,7 +2026,7 @@
     </row>
     <row r="16" spans="1:45" ht="17">
       <c r="A16" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>9</v>
@@ -2040,130 +2035,130 @@
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H16" t="str">
+        <f t="shared" si="6"/>
+        <v>wet</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="15"/>
+        <v>0.34</v>
+      </c>
+      <c r="K16">
         <f t="shared" si="0"/>
-        <v>wet</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16">
+        <v>0.19</v>
+      </c>
+      <c r="L16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="1"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="18"/>
+        <v>7</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="19"/>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="7"/>
+        <v>0.21</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="2"/>
+        <v>0.24</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="3"/>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="4"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="8"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X16">
+        <f t="shared" si="21"/>
+        <v>0.71</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <f t="shared" si="5"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA16">
+        <f t="shared" si="23"/>
+        <v>2.0597580800000003E-4</v>
+      </c>
+      <c r="AB16">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="25"/>
+        <v>0.75181169920000002</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="26"/>
+        <v>7.518116992E-4</v>
+      </c>
+      <c r="AE16">
         <f t="shared" si="9"/>
-        <v>0.34</v>
-      </c>
-      <c r="K16">
-        <f>$AQ$5</f>
-        <v>0.19</v>
-      </c>
-      <c r="L16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M16">
+        <v>25550</v>
+      </c>
+      <c r="AF16">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="N16">
+        <v>0.2409</v>
+      </c>
+      <c r="AG16">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <f>$AN$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P16">
+        <v>5365.5</v>
+      </c>
+      <c r="AH16">
         <f t="shared" si="12"/>
-        <v>7</v>
-      </c>
-      <c r="Q16">
+        <v>2.4451349999999997E-2</v>
+      </c>
+      <c r="AI16">
         <f t="shared" si="13"/>
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S16">
-        <f t="shared" si="1"/>
-        <v>0.21</v>
-      </c>
-      <c r="T16">
-        <f>$AQ$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U16">
-        <f>$AQ$4</f>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V16">
-        <f>$AN$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W16">
-        <f t="shared" si="2"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X16">
-        <f t="shared" si="15"/>
-        <v>0.71</v>
-      </c>
-      <c r="Y16">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <f>$AM$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA16">
-        <f t="shared" si="17"/>
-        <v>2.0597580800000003E-4</v>
-      </c>
-      <c r="AB16">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <f t="shared" si="19"/>
-        <v>0.75181169920000002</v>
-      </c>
-      <c r="AD16">
-        <f t="shared" si="20"/>
-        <v>7.518116992E-4</v>
-      </c>
-      <c r="AE16" s="11">
-        <f t="shared" si="3"/>
-        <v>25550</v>
-      </c>
-      <c r="AF16">
-        <f t="shared" si="4"/>
-        <v>0.2409</v>
-      </c>
-      <c r="AG16">
-        <f t="shared" si="5"/>
-        <v>5365.5</v>
-      </c>
-      <c r="AH16">
-        <f t="shared" si="6"/>
-        <v>2.4451349999999997E-2</v>
-      </c>
-      <c r="AI16">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
       <c r="AM16" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AN16" s="2">
         <v>2.73</v>
@@ -2174,7 +2169,7 @@
       <c r="AP16" s="2"/>
       <c r="AQ16" s="2"/>
       <c r="AR16" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AS16" s="2">
         <v>5.3E-3</v>
@@ -2182,139 +2177,139 @@
     </row>
     <row r="17" spans="1:45" ht="17">
       <c r="A17" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="C17">
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H17" t="str">
+        <f t="shared" si="6"/>
+        <v>dry</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="15"/>
+        <v>0.34</v>
+      </c>
+      <c r="K17">
         <f t="shared" si="0"/>
-        <v>dry</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J17">
+        <v>0.19</v>
+      </c>
+      <c r="L17" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="1"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="18"/>
+        <v>7</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="19"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="7"/>
+        <v>0.21</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="2"/>
+        <v>0.24</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="3"/>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="4"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="8"/>
+        <v>2E-3</v>
+      </c>
+      <c r="X17">
+        <f t="shared" si="21"/>
+        <v>0.75</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <f t="shared" si="5"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA17">
+        <f t="shared" si="23"/>
+        <v>2.0597580800000003E-4</v>
+      </c>
+      <c r="AB17">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <f t="shared" si="25"/>
+        <v>0.82699286912000003</v>
+      </c>
+      <c r="AD17">
+        <f t="shared" si="26"/>
+        <v>8.2699286912000006E-4</v>
+      </c>
+      <c r="AE17">
         <f t="shared" si="9"/>
-        <v>0.34</v>
-      </c>
-      <c r="K17">
-        <f>$AQ$5</f>
-        <v>0.19</v>
-      </c>
-      <c r="L17" t="s">
-        <v>57</v>
-      </c>
-      <c r="M17">
+        <v>28105</v>
+      </c>
+      <c r="AF17">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="N17">
+        <v>8.8330000000000006E-2</v>
+      </c>
+      <c r="AG17">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="O17">
-        <f>$AN$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P17">
+        <v>5902.05</v>
+      </c>
+      <c r="AH17">
         <f t="shared" si="12"/>
-        <v>7</v>
-      </c>
-      <c r="Q17">
+        <v>7.4197199999999991E-2</v>
+      </c>
+      <c r="AI17">
         <f t="shared" si="13"/>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="R17">
+        <v>6745.2</v>
+      </c>
+      <c r="AJ17">
         <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="S17">
-        <f t="shared" si="1"/>
-        <v>0.21</v>
-      </c>
-      <c r="T17">
-        <f>$AQ$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U17">
-        <f>$AQ$4</f>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V17">
-        <f>$AN$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W17">
-        <f t="shared" si="2"/>
-        <v>2E-3</v>
-      </c>
-      <c r="X17">
-        <f t="shared" si="15"/>
-        <v>0.75</v>
-      </c>
-      <c r="Y17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <f>$AM$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA17">
-        <f t="shared" si="17"/>
-        <v>2.0597580800000003E-4</v>
-      </c>
-      <c r="AB17">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <f t="shared" si="19"/>
-        <v>0.82699286912000003</v>
-      </c>
-      <c r="AD17">
-        <f t="shared" si="20"/>
-        <v>8.2699286912000006E-4</v>
-      </c>
-      <c r="AE17" s="11">
-        <f t="shared" si="3"/>
-        <v>28105</v>
-      </c>
-      <c r="AF17">
-        <f t="shared" si="4"/>
-        <v>8.8330000000000006E-2</v>
-      </c>
-      <c r="AG17">
-        <f t="shared" si="5"/>
-        <v>5902.05</v>
-      </c>
-      <c r="AH17">
-        <f t="shared" si="6"/>
-        <v>7.4197199999999991E-2</v>
-      </c>
-      <c r="AI17">
-        <f t="shared" si="7"/>
-        <v>6745.2</v>
-      </c>
-      <c r="AJ17">
-        <f t="shared" si="8"/>
         <v>0.11659559999999999</v>
       </c>
       <c r="AM17" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AN17" s="2">
         <v>0.91</v>
@@ -2325,7 +2320,7 @@
       <c r="AP17" s="2"/>
       <c r="AQ17" s="2"/>
       <c r="AR17" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AS17" s="2">
         <v>6.4000000000000003E-3</v>
@@ -2333,139 +2328,139 @@
     </row>
     <row r="18" spans="1:45" ht="17">
       <c r="A18" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H18" t="str">
+        <f>VLOOKUP(G18,$AR$31:$AS$40,2,FALSE)</f>
+        <v>dry</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J18">
+        <f>VLOOKUP(A18, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.34</v>
+      </c>
+      <c r="K18">
         <f t="shared" si="0"/>
-        <v>dry</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="9"/>
-        <v>0.34</v>
-      </c>
-      <c r="K18">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M18">
-        <f t="shared" si="10"/>
+        <f>1-N18</f>
         <v>0</v>
       </c>
       <c r="N18">
-        <f t="shared" si="11"/>
+        <f>IF(L18="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O18">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P18">
-        <f t="shared" si="12"/>
+        <f>VLOOKUP(A18, $AM$11:$AO$18,3,FALSE)</f>
         <v>7</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="13"/>
-        <v>5.8999999999999999E-3</v>
+        <f>VLOOKUP(E18,$AR$10:$AS$22,2,FALSE)</f>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="R18">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>IF(D18="yes", 1, 0)</f>
+        <v>1</v>
       </c>
       <c r="S18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T18">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U18">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V18">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W18">
-        <f t="shared" si="2"/>
+        <f>IF(H18="wet",$AN$6,$AN$7)</f>
         <v>2E-3</v>
       </c>
       <c r="X18">
-        <f t="shared" si="15"/>
-        <v>0.8</v>
+        <f>VLOOKUP(I18,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.78</v>
       </c>
       <c r="Y18">
-        <f t="shared" si="16"/>
+        <f>J18*K18*M18*X18*V18</f>
         <v>0</v>
       </c>
       <c r="Z18">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA18">
-        <f t="shared" si="17"/>
+        <f>J18*K18*N18*Z18*V18</f>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB18">
-        <f t="shared" si="18"/>
+        <f>C18*Y18*365</f>
         <v>0</v>
       </c>
       <c r="AC18">
-        <f t="shared" si="19"/>
-        <v>0.90217403904000026</v>
+        <f>C18*AA18*365</f>
+        <v>0.97735520896000017</v>
       </c>
       <c r="AD18">
-        <f t="shared" si="20"/>
-        <v>9.0217403904000024E-4</v>
-      </c>
-      <c r="AE18" s="11">
-        <f t="shared" si="3"/>
-        <v>30660</v>
+        <f>(AB18+AC18)*10^-3</f>
+        <v>9.7735520896000019E-4</v>
+      </c>
+      <c r="AE18">
+        <f>C18*P18*365</f>
+        <v>33215</v>
       </c>
       <c r="AF18">
-        <f t="shared" si="4"/>
-        <v>9.6360000000000001E-2</v>
+        <f>AE18*W18*O18*10^-3</f>
+        <v>0.10439000000000001</v>
       </c>
       <c r="AG18">
-        <f t="shared" si="5"/>
-        <v>6438.5999999999995</v>
+        <f>AE18*S18</f>
+        <v>6975.15</v>
       </c>
       <c r="AH18">
-        <f t="shared" si="6"/>
-        <v>5.9695019999999994E-2</v>
+        <f>AG18*Q18*O18*10^-3</f>
+        <v>7.6726649999999993E-2</v>
       </c>
       <c r="AI18">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AE18*R18*T18</f>
+        <v>7971.5999999999995</v>
       </c>
       <c r="AJ18">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>AI18*U18*O18*10^-3</f>
+        <v>0.1377948</v>
       </c>
       <c r="AM18" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AN18" s="2">
         <v>0.34</v>
@@ -2476,7 +2471,7 @@
       <c r="AP18" s="2"/>
       <c r="AQ18" s="10"/>
       <c r="AR18" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AS18" s="2">
         <v>2.5999999999999999E-3</v>
@@ -2484,141 +2479,141 @@
     </row>
     <row r="19" spans="1:45" ht="17">
       <c r="A19" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H19" t="str">
+        <f>VLOOKUP(G19,$AR$31:$AS$40,2,FALSE)</f>
+        <v>dry</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19">
+        <f>VLOOKUP(A19, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.34</v>
+      </c>
+      <c r="K19">
         <f t="shared" si="0"/>
-        <v>dry</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="9"/>
-        <v>0.34</v>
-      </c>
-      <c r="K19">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M19">
-        <f t="shared" si="10"/>
+        <f>1-N19</f>
         <v>0</v>
       </c>
       <c r="N19">
-        <f t="shared" si="11"/>
+        <f>IF(L19="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O19">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P19">
-        <f t="shared" si="12"/>
+        <f>VLOOKUP(A19, $AM$11:$AO$18,3,FALSE)</f>
         <v>7</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="13"/>
-        <v>7.0000000000000001E-3</v>
+        <f>VLOOKUP(E19,$AR$10:$AS$22,2,FALSE)</f>
+        <v>1.8E-3</v>
       </c>
       <c r="R19">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f>IF(D19="yes", 1, 0)</f>
+        <v>0</v>
       </c>
       <c r="S19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T19">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U19">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V19">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W19">
-        <f t="shared" si="2"/>
+        <f>IF(H19="wet",$AN$6,$AN$7)</f>
         <v>2E-3</v>
       </c>
       <c r="X19">
-        <f t="shared" si="15"/>
-        <v>0.78</v>
+        <f>VLOOKUP(I19,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.74</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="16"/>
+        <f>J19*K19*M19*X19*V19</f>
         <v>0</v>
       </c>
       <c r="Z19">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA19">
-        <f t="shared" si="17"/>
+        <f>J19*K19*N19*Z19*V19</f>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB19">
-        <f t="shared" si="18"/>
+        <f>C19*Y19*365</f>
         <v>0</v>
       </c>
       <c r="AC19">
-        <f t="shared" si="19"/>
-        <v>0.97735520896000017</v>
+        <f>C19*AA19*365</f>
+        <v>1.0525363788800002</v>
       </c>
       <c r="AD19">
-        <f t="shared" si="20"/>
-        <v>9.7735520896000019E-4</v>
-      </c>
-      <c r="AE19" s="11">
-        <f t="shared" si="3"/>
-        <v>33215</v>
+        <f>(AB19+AC19)*10^-3</f>
+        <v>1.0525363788800003E-3</v>
+      </c>
+      <c r="AE19">
+        <f>C19*P19*365</f>
+        <v>35770</v>
       </c>
       <c r="AF19">
-        <f t="shared" si="4"/>
-        <v>0.10439000000000001</v>
+        <f>AE19*W19*O19*10^-3</f>
+        <v>0.11242000000000001</v>
       </c>
       <c r="AG19">
-        <f t="shared" si="5"/>
-        <v>6975.15</v>
+        <f>AE19*S19</f>
+        <v>7511.7</v>
       </c>
       <c r="AH19">
-        <f t="shared" si="6"/>
-        <v>7.6726649999999993E-2</v>
+        <f>AG19*Q19*O19*10^-3</f>
+        <v>2.1247379999999996E-2</v>
       </c>
       <c r="AI19">
-        <f t="shared" si="7"/>
-        <v>7971.5999999999995</v>
+        <f>AE19*R19*T19</f>
+        <v>0</v>
       </c>
       <c r="AJ19">
-        <f t="shared" si="8"/>
-        <v>0.1377948</v>
+        <f>AI19*U19*O19*10^-3</f>
+        <v>0</v>
       </c>
       <c r="AP19" s="2"/>
       <c r="AQ19" s="10"/>
       <c r="AR19" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AS19" s="2">
         <v>3.0000000000000001E-3</v>
@@ -2626,141 +2621,141 @@
     </row>
     <row r="20" spans="1:45" ht="17">
       <c r="A20" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H20" t="str">
+        <f>VLOOKUP(G20,$AR$31:$AS$40,2,FALSE)</f>
+        <v>wet</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J20">
+        <f>VLOOKUP(A20, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.34</v>
+      </c>
+      <c r="K20">
         <f t="shared" si="0"/>
-        <v>dry</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="9"/>
-        <v>0.34</v>
-      </c>
-      <c r="K20">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M20">
-        <f t="shared" si="10"/>
+        <f>1-N20</f>
         <v>0</v>
       </c>
       <c r="N20">
-        <f t="shared" si="11"/>
+        <f>IF(L20="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O20">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P20">
-        <f t="shared" si="12"/>
+        <f>VLOOKUP(A20, $AM$11:$AO$18,3,FALSE)</f>
         <v>7</v>
       </c>
       <c r="Q20">
-        <f t="shared" si="13"/>
-        <v>1.8E-3</v>
+        <f>VLOOKUP(E20,$AR$10:$AS$22,2,FALSE)</f>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="R20">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>IF(D20="yes", 1, 0)</f>
+        <v>1</v>
       </c>
       <c r="S20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T20">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U20">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V20">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W20">
-        <f t="shared" si="2"/>
-        <v>2E-3</v>
+        <f>IF(H20="wet",$AN$6,$AN$7)</f>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="X20">
-        <f t="shared" si="15"/>
-        <v>0.74</v>
+        <f>VLOOKUP(I20,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.7</v>
       </c>
       <c r="Y20">
-        <f t="shared" si="16"/>
+        <f>J20*K20*M20*X20*V20</f>
         <v>0</v>
       </c>
       <c r="Z20">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA20">
-        <f t="shared" si="17"/>
+        <f>J20*K20*N20*Z20*V20</f>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB20">
-        <f t="shared" si="18"/>
+        <f>C20*Y20*365</f>
         <v>0</v>
       </c>
       <c r="AC20">
-        <f t="shared" si="19"/>
-        <v>1.0525363788800002</v>
+        <f>C20*AA20*365</f>
+        <v>1.1277175488000002</v>
       </c>
       <c r="AD20">
-        <f t="shared" si="20"/>
-        <v>1.0525363788800003E-3</v>
-      </c>
-      <c r="AE20" s="11">
-        <f t="shared" si="3"/>
-        <v>35770</v>
+        <f>(AB20+AC20)*10^-3</f>
+        <v>1.1277175488000003E-3</v>
+      </c>
+      <c r="AE20">
+        <f>C20*P20*365</f>
+        <v>38325</v>
       </c>
       <c r="AF20">
-        <f t="shared" si="4"/>
-        <v>0.11242000000000001</v>
+        <f>AE20*W20*O20*10^-3</f>
+        <v>0.36135</v>
       </c>
       <c r="AG20">
-        <f t="shared" si="5"/>
-        <v>7511.7</v>
+        <f>AE20*S20</f>
+        <v>8048.25</v>
       </c>
       <c r="AH20">
-        <f t="shared" si="6"/>
-        <v>2.1247379999999996E-2</v>
+        <f>AG20*Q20*O20*10^-3</f>
+        <v>3.6677024999999995E-2</v>
       </c>
       <c r="AI20">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AE20*R20*T20</f>
+        <v>9198</v>
       </c>
       <c r="AJ20">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>AI20*U20*O20*10^-3</f>
+        <v>0.158994</v>
       </c>
       <c r="AP20" s="2"/>
       <c r="AQ20" s="2"/>
       <c r="AR20" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AS20" s="2">
         <v>5.0000000000000001E-3</v>
@@ -2768,147 +2763,147 @@
     </row>
     <row r="21" spans="1:45" ht="17">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H21" t="str">
+        <f>VLOOKUP(G21,$AR$31:$AS$40,2,FALSE)</f>
+        <v>wet</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21">
+        <f>VLOOKUP(A21, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.91</v>
+      </c>
+      <c r="K21">
         <f t="shared" si="0"/>
-        <v>wet</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="9"/>
-        <v>0.34</v>
-      </c>
-      <c r="K21">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M21">
-        <f t="shared" si="10"/>
+        <f>1-N21</f>
         <v>0</v>
       </c>
       <c r="N21">
-        <f t="shared" si="11"/>
+        <f>IF(L21="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O21">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P21">
-        <f t="shared" si="12"/>
-        <v>7</v>
+        <f>VLOOKUP(A21, $AM$11:$AO$18,3,FALSE)</f>
+        <v>13.2</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="13"/>
-        <v>2.8999999999999998E-3</v>
+        <f>VLOOKUP(E21,$AR$10:$AS$22,2,FALSE)</f>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="R21">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f>IF(D21="yes", 1, 0)</f>
+        <v>0</v>
       </c>
       <c r="S21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T21">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U21">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V21">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W21">
-        <f t="shared" si="2"/>
+        <f>IF(H21="wet",$AN$6,$AN$7)</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X21">
-        <f t="shared" si="15"/>
-        <v>0.7</v>
+        <f>VLOOKUP(I21,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.74</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="16"/>
+        <f>J21*K21*M21*X21*V21</f>
         <v>0</v>
       </c>
       <c r="Z21">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA21">
-        <f t="shared" si="17"/>
-        <v>2.0597580800000003E-4</v>
+        <f>J21*K21*N21*Z21*V21</f>
+        <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="18"/>
+        <f>C21*Y21*365</f>
         <v>0</v>
       </c>
       <c r="AC21">
-        <f t="shared" si="19"/>
-        <v>1.1277175488000002</v>
+        <f>C21*AA21*365</f>
+        <v>3.21952304128</v>
       </c>
       <c r="AD21">
-        <f t="shared" si="20"/>
-        <v>1.1277175488000003E-3</v>
-      </c>
-      <c r="AE21" s="11">
-        <f t="shared" si="3"/>
-        <v>38325</v>
+        <f>(AB21+AC21)*10^-3</f>
+        <v>3.21952304128E-3</v>
+      </c>
+      <c r="AE21">
+        <f>C21*P21*365</f>
+        <v>77088</v>
       </c>
       <c r="AF21">
-        <f t="shared" si="4"/>
-        <v>0.36135</v>
+        <f>AE21*W21*O21*10^-3</f>
+        <v>0.7268297142857143</v>
       </c>
       <c r="AG21">
-        <f t="shared" si="5"/>
-        <v>8048.25</v>
+        <f>AE21*S21</f>
+        <v>16188.48</v>
       </c>
       <c r="AH21">
-        <f t="shared" si="6"/>
-        <v>3.6677024999999995E-2</v>
+        <f>AG21*Q21*O21*10^-3</f>
+        <v>0.20351232</v>
       </c>
       <c r="AI21">
-        <f t="shared" si="7"/>
-        <v>9198</v>
+        <f>AE21*R21*T21</f>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <f t="shared" si="8"/>
-        <v>0.158994</v>
+        <f>AI21*U21*O21*10^-3</f>
+        <v>0</v>
       </c>
       <c r="AM21" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AN21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP21" s="2"/>
       <c r="AQ21" s="2"/>
       <c r="AR21" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AS21" s="2">
         <v>2.5999999999999999E-3</v>
@@ -2916,142 +2911,142 @@
     </row>
     <row r="22" spans="1:45" ht="17">
       <c r="A22" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H22" t="str">
+        <f>VLOOKUP(G22,$AR$31:$AS$40,2,FALSE)</f>
+        <v>wet</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J22">
+        <f>VLOOKUP(A22, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.91</v>
+      </c>
+      <c r="K22">
         <f t="shared" si="0"/>
-        <v>wet</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="9"/>
-        <v>0.91</v>
-      </c>
-      <c r="K22">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M22">
-        <f t="shared" si="10"/>
+        <f>1-N22</f>
         <v>0</v>
       </c>
       <c r="N22">
-        <f t="shared" si="11"/>
+        <f>IF(L22="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O22">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P22">
-        <f t="shared" si="12"/>
+        <f>VLOOKUP(A22, $AM$11:$AO$18,3,FALSE)</f>
         <v>13.2</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="13"/>
-        <v>8.0000000000000002E-3</v>
+        <f>VLOOKUP(E22,$AR$10:$AS$22,2,FALSE)</f>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="R22">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>IF(D22="yes", 1, 0)</f>
+        <v>1</v>
       </c>
       <c r="S22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T22">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U22">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V22">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W22">
-        <f t="shared" si="2"/>
+        <f>IF(H22="wet",$AN$6,$AN$7)</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X22">
-        <f t="shared" si="15"/>
-        <v>0.74</v>
+        <f>VLOOKUP(I22,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.76</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="16"/>
+        <f>J22*K22*M22*X22*V22</f>
         <v>0</v>
       </c>
       <c r="Z22">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="17"/>
+        <f>J22*K22*N22*Z22*V22</f>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB22">
-        <f t="shared" si="18"/>
+        <f>C22*Y22*365</f>
         <v>0</v>
       </c>
       <c r="AC22">
-        <f t="shared" si="19"/>
-        <v>3.21952304128</v>
+        <f>C22*AA22*365</f>
+        <v>3.4207432313599999</v>
       </c>
       <c r="AD22">
-        <f t="shared" si="20"/>
-        <v>3.21952304128E-3</v>
-      </c>
-      <c r="AE22" s="11">
-        <f t="shared" si="3"/>
-        <v>77088</v>
+        <f>(AB22+AC22)*10^-3</f>
+        <v>3.4207432313600001E-3</v>
+      </c>
+      <c r="AE22">
+        <f>C22*P22*365</f>
+        <v>81905.999999999985</v>
       </c>
       <c r="AF22">
-        <f t="shared" si="4"/>
-        <v>0.7268297142857143</v>
+        <f>AE22*W22*O22*10^-3</f>
+        <v>0.77225657142857129</v>
       </c>
       <c r="AG22">
-        <f t="shared" si="5"/>
-        <v>16188.48</v>
+        <f>AE22*S22</f>
+        <v>17200.259999999995</v>
       </c>
       <c r="AH22">
-        <f t="shared" si="6"/>
-        <v>0.20351232</v>
+        <f>AG22*Q22*O22*10^-3</f>
+        <v>0.15947098199999993</v>
       </c>
       <c r="AI22">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AE22*R22*T22</f>
+        <v>19657.439999999995</v>
       </c>
       <c r="AJ22">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>AI22*U22*O22*10^-3</f>
+        <v>0.33979289142857128</v>
       </c>
       <c r="AM22" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AR22" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AS22" s="2">
         <v>1.8E-3</v>
@@ -3059,139 +3054,139 @@
     </row>
     <row r="23" spans="1:45" ht="17">
       <c r="A23" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H23" t="str">
+        <f>VLOOKUP(G23,$AR$31:$AS$40,2,FALSE)</f>
+        <v>wet</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23">
+        <f>VLOOKUP(A23, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.91</v>
+      </c>
+      <c r="K23">
         <f t="shared" si="0"/>
-        <v>wet</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="9"/>
-        <v>0.91</v>
-      </c>
-      <c r="K23">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M23">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>1-N23</f>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="N23">
-        <f t="shared" si="11"/>
-        <v>1</v>
+        <f>IF(L23="yes", 1, 0.95)</f>
+        <v>0.95</v>
       </c>
       <c r="O23">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P23">
-        <f t="shared" si="12"/>
+        <f>VLOOKUP(A23, $AM$11:$AO$18,3,FALSE)</f>
         <v>13.2</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="13"/>
-        <v>5.8999999999999999E-3</v>
+        <f>VLOOKUP(E23,$AR$10:$AS$22,2,FALSE)</f>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="R23">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f>IF(D23="yes", 1, 0)</f>
+        <v>0</v>
       </c>
       <c r="S23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T23">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U23">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V23">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W23">
-        <f t="shared" si="2"/>
+        <f>IF(H23="wet",$AN$6,$AN$7)</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X23">
-        <f t="shared" si="15"/>
-        <v>0.76</v>
+        <f>VLOOKUP(I23,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.71</v>
       </c>
       <c r="Y23">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>J23*K23*M23*X23*V23</f>
+        <v>4.1639852800000035E-3</v>
       </c>
       <c r="Z23">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA23">
-        <f t="shared" si="17"/>
-        <v>5.5128819200000003E-4</v>
+        <f>J23*K23*N23*Z23*V23</f>
+        <v>5.2372378239999996E-4</v>
       </c>
       <c r="AB23">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>C23*Y23*365</f>
+        <v>27.357383289600023</v>
       </c>
       <c r="AC23">
-        <f t="shared" si="19"/>
-        <v>3.4207432313599999</v>
+        <f>C23*AA23*365</f>
+        <v>3.4408652503679997</v>
       </c>
       <c r="AD23">
-        <f t="shared" si="20"/>
-        <v>3.4207432313600001E-3</v>
-      </c>
-      <c r="AE23" s="11">
-        <f t="shared" si="3"/>
-        <v>81905.999999999985</v>
+        <f>(AB23+AC23)*10^-3</f>
+        <v>3.0798248539968022E-2</v>
+      </c>
+      <c r="AE23">
+        <f>C23*P23*365</f>
+        <v>86724</v>
       </c>
       <c r="AF23">
-        <f t="shared" si="4"/>
-        <v>0.77225657142857129</v>
+        <f>AE23*W23*O23*10^-3</f>
+        <v>0.81768342857142862</v>
       </c>
       <c r="AG23">
-        <f t="shared" si="5"/>
-        <v>17200.259999999995</v>
+        <f>AE23*S23</f>
+        <v>18212.04</v>
       </c>
       <c r="AH23">
-        <f t="shared" si="6"/>
-        <v>0.15947098199999993</v>
+        <f>AG23*Q23*O23*10^-3</f>
+        <v>0.20033244000000003</v>
       </c>
       <c r="AI23">
-        <f t="shared" si="7"/>
-        <v>19657.439999999995</v>
+        <f>AE23*R23*T23</f>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <f t="shared" si="8"/>
-        <v>0.33979289142857128</v>
+        <f>AI23*U23*O23*10^-3</f>
+        <v>0</v>
       </c>
       <c r="AM23" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AN23" s="2">
         <v>0.71</v>
@@ -3200,139 +3195,139 @@
     </row>
     <row r="24" spans="1:45" ht="17">
       <c r="A24" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H24" t="str">
+        <f>VLOOKUP(G24,$AR$31:$AS$40,2,FALSE)</f>
+        <v>wet</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J24">
+        <f>VLOOKUP(A24, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.91</v>
+      </c>
+      <c r="K24">
         <f t="shared" si="0"/>
-        <v>wet</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J24">
-        <f t="shared" si="9"/>
-        <v>0.91</v>
-      </c>
-      <c r="K24">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L24" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M24">
-        <f t="shared" si="10"/>
+        <f>1-N24</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N24">
-        <f t="shared" si="11"/>
+        <f>IF(L24="yes", 1, 0.95)</f>
         <v>0.95</v>
       </c>
       <c r="O24">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P24">
-        <f t="shared" si="12"/>
+        <f>VLOOKUP(A24, $AM$11:$AO$18,3,FALSE)</f>
         <v>13.2</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="13"/>
-        <v>7.0000000000000001E-3</v>
+        <f>VLOOKUP(E24,$AR$10:$AS$22,2,FALSE)</f>
+        <v>1.8E-3</v>
       </c>
       <c r="R24">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>IF(D24="yes", 1, 0)</f>
+        <v>1</v>
       </c>
       <c r="S24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T24">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U24">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V24">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W24">
-        <f t="shared" si="2"/>
+        <f>IF(H24="wet",$AN$6,$AN$7)</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X24">
-        <f t="shared" si="15"/>
-        <v>0.71</v>
+        <f>VLOOKUP(I24,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.75</v>
       </c>
       <c r="Y24">
-        <f t="shared" si="16"/>
-        <v>4.1639852800000035E-3</v>
+        <f>J24*K24*M24*X24*V24</f>
+        <v>4.3985760000000039E-3</v>
       </c>
       <c r="Z24">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA24">
-        <f t="shared" si="17"/>
+        <f>J24*K24*N24*Z24*V24</f>
         <v>5.2372378239999996E-4</v>
       </c>
       <c r="AB24">
-        <f t="shared" si="18"/>
-        <v>27.357383289600023</v>
+        <f>C24*Y24*365</f>
+        <v>30.504124560000029</v>
       </c>
       <c r="AC24">
-        <f t="shared" si="19"/>
-        <v>3.4408652503679997</v>
+        <f>C24*AA24*365</f>
+        <v>3.6320244309439995</v>
       </c>
       <c r="AD24">
-        <f t="shared" si="20"/>
-        <v>3.0798248539968022E-2</v>
-      </c>
-      <c r="AE24" s="11">
-        <f t="shared" si="3"/>
-        <v>86724</v>
+        <f>(AB24+AC24)*10^-3</f>
+        <v>3.4136148990944033E-2</v>
+      </c>
+      <c r="AE24">
+        <f>C24*P24*365</f>
+        <v>91542</v>
       </c>
       <c r="AF24">
-        <f t="shared" si="4"/>
-        <v>0.81768342857142862</v>
+        <f>AE24*W24*O24*10^-3</f>
+        <v>0.86311028571428583</v>
       </c>
       <c r="AG24">
-        <f t="shared" si="5"/>
-        <v>18212.04</v>
+        <f>AE24*S24</f>
+        <v>19223.82</v>
       </c>
       <c r="AH24">
-        <f t="shared" si="6"/>
-        <v>0.20033244000000003</v>
+        <f>AG24*Q24*O24*10^-3</f>
+        <v>5.4375948E-2</v>
       </c>
       <c r="AI24">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AE24*R24*T24</f>
+        <v>21970.079999999998</v>
       </c>
       <c r="AJ24">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>AI24*U24*O24*10^-3</f>
+        <v>0.37976852571428565</v>
       </c>
       <c r="AM24" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AN24" s="2">
         <v>0.75</v>
@@ -3340,141 +3335,141 @@
       <c r="AP24" s="2"/>
       <c r="AQ24" s="2"/>
     </row>
-    <row r="25" spans="1:45" ht="17">
-      <c r="A25" s="3" t="s">
-        <v>24</v>
+    <row r="25" spans="1:45">
+      <c r="A25" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H25" t="str">
+        <f>VLOOKUP(G25,$AR$31:$AS$40,2,FALSE)</f>
+        <v>wet</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J25">
+        <f>VLOOKUP(A25, $AM$11:$AN$18,2,FALSE)</f>
+        <v>2.73</v>
+      </c>
+      <c r="K25">
         <f t="shared" si="0"/>
-        <v>wet</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J25">
-        <f t="shared" si="9"/>
-        <v>0.91</v>
-      </c>
-      <c r="K25">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M25">
-        <f t="shared" si="10"/>
+        <f>1-N25</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N25">
-        <f t="shared" si="11"/>
+        <f>IF(L25="yes", 1, 0.95)</f>
         <v>0.95</v>
       </c>
       <c r="O25">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P25">
-        <f t="shared" si="12"/>
-        <v>13.2</v>
+        <f>VLOOKUP(A25, $AM$11:$AO$18,3,FALSE)</f>
+        <v>39.5</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="13"/>
-        <v>1.8E-3</v>
+        <f>VLOOKUP(E25,$AR$10:$AS$22,2,FALSE)</f>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="R25">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f>IF(D25="yes", 1, 0)</f>
+        <v>0</v>
       </c>
       <c r="S25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T25">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U25">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V25">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W25">
-        <f t="shared" si="2"/>
+        <f>IF(H25="wet",$AN$6,$AN$7)</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X25">
-        <f t="shared" si="15"/>
-        <v>0.75</v>
+        <f>VLOOKUP(I25,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.8</v>
       </c>
       <c r="Y25">
-        <f t="shared" si="16"/>
-        <v>4.3985760000000039E-3</v>
+        <f>J25*K25*M25*X25*V25</f>
+        <v>1.4075443200000013E-2</v>
       </c>
       <c r="Z25">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA25">
-        <f t="shared" si="17"/>
-        <v>5.2372378239999996E-4</v>
+        <f>J25*K25*N25*Z25*V25</f>
+        <v>1.5711713472E-3</v>
       </c>
       <c r="AB25">
-        <f t="shared" si="18"/>
-        <v>30.504124560000029</v>
+        <f>C25*Y25*365</f>
+        <v>102.75073536000009</v>
       </c>
       <c r="AC25">
-        <f t="shared" si="19"/>
-        <v>3.6320244309439995</v>
+        <f>C25*AA25*365</f>
+        <v>11.46955083456</v>
       </c>
       <c r="AD25">
-        <f t="shared" si="20"/>
-        <v>3.4136148990944033E-2</v>
-      </c>
-      <c r="AE25" s="11">
-        <f t="shared" si="3"/>
-        <v>91542</v>
+        <f>(AB25+AC25)*10^-3</f>
+        <v>0.11422028619456009</v>
+      </c>
+      <c r="AE25">
+        <f>C25*P25*365</f>
+        <v>288350</v>
       </c>
       <c r="AF25">
-        <f t="shared" si="4"/>
-        <v>0.86311028571428583</v>
+        <f>AE25*W25*O25*10^-3</f>
+        <v>2.7187285714285716</v>
       </c>
       <c r="AG25">
-        <f t="shared" si="5"/>
-        <v>19223.82</v>
+        <f>AE25*S25</f>
+        <v>60553.5</v>
       </c>
       <c r="AH25">
-        <f t="shared" si="6"/>
-        <v>5.4375948E-2</v>
+        <f>AG25*Q25*O25*10^-3</f>
+        <v>0.27595094999999997</v>
       </c>
       <c r="AI25">
-        <f t="shared" si="7"/>
-        <v>21970.079999999998</v>
+        <f>AE25*R25*T25</f>
+        <v>0</v>
       </c>
       <c r="AJ25">
-        <f t="shared" si="8"/>
-        <v>0.37976852571428565</v>
+        <f>AI25*U25*O25*10^-3</f>
+        <v>0</v>
       </c>
       <c r="AM25" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AN25" s="2">
         <v>0.8</v>
@@ -3484,139 +3479,139 @@
     </row>
     <row r="26" spans="1:45">
       <c r="A26" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H26" t="str">
+        <f>VLOOKUP(G26,$AR$31:$AS$40,2,FALSE)</f>
+        <v>dry</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J26">
+        <f>VLOOKUP(A26, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.34</v>
+      </c>
+      <c r="K26">
         <f t="shared" si="0"/>
-        <v>wet</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J26">
-        <f t="shared" si="9"/>
-        <v>2.73</v>
-      </c>
-      <c r="K26">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M26">
-        <f t="shared" si="10"/>
+        <f>1-N26</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N26">
-        <f t="shared" si="11"/>
+        <f>IF(L26="yes", 1, 0.95)</f>
         <v>0.95</v>
       </c>
       <c r="O26">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P26">
-        <f t="shared" si="12"/>
-        <v>39.5</v>
+        <f>VLOOKUP(A26, $AM$11:$AO$18,3,FALSE)</f>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="13"/>
-        <v>2.8999999999999998E-3</v>
+        <f>VLOOKUP(E26,$AR$10:$AS$22,2,FALSE)</f>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="R26">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>IF(D26="yes", 1, 0)</f>
+        <v>1</v>
       </c>
       <c r="S26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T26">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U26">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V26">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W26">
-        <f t="shared" si="2"/>
-        <v>6.0000000000000001E-3</v>
+        <f>IF(H26="wet",$AN$6,$AN$7)</f>
+        <v>2E-3</v>
       </c>
       <c r="X26">
-        <f t="shared" si="15"/>
-        <v>0.8</v>
+        <f>VLOOKUP(I26,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.78</v>
       </c>
       <c r="Y26">
-        <f t="shared" si="16"/>
-        <v>1.4075443200000013E-2</v>
+        <f>J26*K26*M26*X26*V26</f>
+        <v>1.709160960000002E-3</v>
       </c>
       <c r="Z26">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA26">
-        <f t="shared" si="17"/>
-        <v>1.5711713472E-3</v>
+        <f>J26*K26*N26*Z26*V26</f>
+        <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB26">
-        <f t="shared" si="18"/>
-        <v>102.75073536000009</v>
+        <f>C26*Y26*365</f>
+        <v>13.100718758400015</v>
       </c>
       <c r="AC26">
-        <f t="shared" si="19"/>
-        <v>11.46955083456</v>
+        <f>C26*AA26*365</f>
+        <v>1.4998643399039999</v>
       </c>
       <c r="AD26">
-        <f t="shared" si="20"/>
-        <v>0.11422028619456009</v>
-      </c>
-      <c r="AE26" s="11">
-        <f t="shared" si="3"/>
-        <v>288350</v>
+        <f>(AB26+AC26)*10^-3</f>
+        <v>1.4600583098304016E-2</v>
+      </c>
+      <c r="AE26">
+        <f>C26*P26*365</f>
+        <v>53655</v>
       </c>
       <c r="AF26">
-        <f t="shared" si="4"/>
-        <v>2.7187285714285716</v>
+        <f>AE26*W26*O26*10^-3</f>
+        <v>0.16863</v>
       </c>
       <c r="AG26">
-        <f t="shared" si="5"/>
-        <v>60553.5</v>
+        <f>AE26*S26</f>
+        <v>11267.55</v>
       </c>
       <c r="AH26">
-        <f t="shared" si="6"/>
-        <v>0.27595094999999997</v>
+        <f>AG26*Q26*O26*10^-3</f>
+        <v>0.1416492</v>
       </c>
       <c r="AI26">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AE26*R26*T26</f>
+        <v>12877.199999999999</v>
       </c>
       <c r="AJ26">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>AI26*U26*O26*10^-3</f>
+        <v>0.22259159999999997</v>
       </c>
       <c r="AM26" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AN26" s="2">
         <v>0.78</v>
@@ -3626,139 +3621,139 @@
     </row>
     <row r="27" spans="1:45">
       <c r="A27" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H27" t="str">
+        <f>VLOOKUP(G27,$AR$31:$AS$40,2,FALSE)</f>
+        <v>dry</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J27">
+        <f>VLOOKUP(A27, $AM$11:$AN$18,2,FALSE)</f>
+        <v>2.73</v>
+      </c>
+      <c r="K27">
         <f t="shared" si="0"/>
-        <v>dry</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J27">
-        <f t="shared" si="9"/>
-        <v>0.34</v>
-      </c>
-      <c r="K27">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M27">
-        <f t="shared" si="10"/>
+        <f>1-N27</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N27">
-        <f t="shared" si="11"/>
+        <f>IF(L27="yes", 1, 0.95)</f>
         <v>0.95</v>
       </c>
       <c r="O27">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P27">
-        <f t="shared" si="12"/>
-        <v>7</v>
+        <f>VLOOKUP(A27, $AM$11:$AO$18,3,FALSE)</f>
+        <v>39.5</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="13"/>
-        <v>8.0000000000000002E-3</v>
+        <f>VLOOKUP(E27,$AR$10:$AS$22,2,FALSE)</f>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="R27">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f>IF(D27="yes", 1, 0)</f>
+        <v>0</v>
       </c>
       <c r="S27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T27">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U27">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V27">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W27">
-        <f t="shared" si="2"/>
+        <f>IF(H27="wet",$AN$6,$AN$7)</f>
         <v>2E-3</v>
       </c>
       <c r="X27">
-        <f t="shared" si="15"/>
-        <v>0.78</v>
+        <f>VLOOKUP(I27,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.74</v>
       </c>
       <c r="Y27">
-        <f t="shared" si="16"/>
-        <v>1.709160960000002E-3</v>
+        <f>J27*K27*M27*X27*V27</f>
+        <v>1.3019784960000013E-2</v>
       </c>
       <c r="Z27">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA27">
-        <f t="shared" si="17"/>
-        <v>1.9567701760000002E-4</v>
+        <f>J27*K27*N27*Z27*V27</f>
+        <v>1.5711713472E-3</v>
       </c>
       <c r="AB27">
-        <f t="shared" si="18"/>
-        <v>13.100718758400015</v>
+        <f>C27*Y27*365</f>
+        <v>104.5488732288001</v>
       </c>
       <c r="AC27">
-        <f t="shared" si="19"/>
-        <v>1.4998643399039999</v>
+        <f>C27*AA27*365</f>
+        <v>12.616505918016001</v>
       </c>
       <c r="AD27">
-        <f t="shared" si="20"/>
-        <v>1.4600583098304016E-2</v>
-      </c>
-      <c r="AE27" s="11">
-        <f t="shared" si="3"/>
-        <v>53655</v>
+        <f>(AB27+AC27)*10^-3</f>
+        <v>0.11716537914681611</v>
+      </c>
+      <c r="AE27">
+        <f>C27*P27*365</f>
+        <v>317185</v>
       </c>
       <c r="AF27">
-        <f t="shared" si="4"/>
-        <v>0.16863</v>
+        <f>AE27*W27*O27*10^-3</f>
+        <v>0.99686714285714295</v>
       </c>
       <c r="AG27">
-        <f t="shared" si="5"/>
-        <v>11267.55</v>
+        <f>AE27*S27</f>
+        <v>66608.849999999991</v>
       </c>
       <c r="AH27">
-        <f t="shared" si="6"/>
-        <v>0.1416492</v>
+        <f>AG27*Q27*O27*10^-3</f>
+        <v>0.61755919499999989</v>
       </c>
       <c r="AI27">
-        <f t="shared" si="7"/>
-        <v>12877.199999999999</v>
+        <f>AE27*R27*T27</f>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <f t="shared" si="8"/>
-        <v>0.22259159999999997</v>
+        <f>AI27*U27*O27*10^-3</f>
+        <v>0</v>
       </c>
       <c r="AM27" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AN27" s="2">
         <v>0.74</v>
@@ -3768,139 +3763,139 @@
     </row>
     <row r="28" spans="1:45">
       <c r="A28" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C28">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H28" t="str">
+        <f>VLOOKUP(G28,$AR$31:$AS$40,2,FALSE)</f>
+        <v>dry</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J28">
+        <f>VLOOKUP(A28, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.91</v>
+      </c>
+      <c r="K28">
         <f t="shared" si="0"/>
-        <v>dry</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J28">
-        <f t="shared" si="9"/>
-        <v>2.73</v>
-      </c>
-      <c r="K28">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M28">
-        <f t="shared" si="10"/>
+        <f>1-N28</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N28">
-        <f t="shared" si="11"/>
+        <f>IF(L28="yes", 1, 0.95)</f>
         <v>0.95</v>
       </c>
       <c r="O28">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P28">
-        <f t="shared" si="12"/>
-        <v>39.5</v>
+        <f>VLOOKUP(A28, $AM$11:$AO$18,3,FALSE)</f>
+        <v>13.2</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="13"/>
-        <v>5.8999999999999999E-3</v>
+        <f>VLOOKUP(E28,$AR$10:$AS$22,2,FALSE)</f>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="R28">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>IF(D28="yes", 1, 0)</f>
+        <v>1</v>
       </c>
       <c r="S28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T28">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U28">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V28">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W28">
-        <f t="shared" si="2"/>
+        <f>IF(H28="wet",$AN$6,$AN$7)</f>
         <v>2E-3</v>
       </c>
       <c r="X28">
-        <f t="shared" si="15"/>
-        <v>0.74</v>
+        <f>VLOOKUP(I28,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.7</v>
       </c>
       <c r="Y28">
-        <f t="shared" si="16"/>
-        <v>1.3019784960000013E-2</v>
+        <f>J28*K28*M28*X28*V28</f>
+        <v>4.1053376000000034E-3</v>
       </c>
       <c r="Z28">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA28">
-        <f t="shared" si="17"/>
-        <v>1.5711713472E-3</v>
+        <f>J28*K28*N28*Z28*V28</f>
+        <v>5.2372378239999996E-4</v>
       </c>
       <c r="AB28">
-        <f t="shared" si="18"/>
-        <v>104.5488732288001</v>
+        <f>C28*Y28*365</f>
+        <v>34.464309152000027</v>
       </c>
       <c r="AC28">
-        <f t="shared" si="19"/>
-        <v>12.616505918016001</v>
+        <f>C28*AA28*365</f>
+        <v>4.396661153248</v>
       </c>
       <c r="AD28">
-        <f t="shared" si="20"/>
-        <v>0.11716537914681611</v>
-      </c>
-      <c r="AE28" s="11">
-        <f t="shared" si="3"/>
-        <v>317185</v>
+        <f>(AB28+AC28)*10^-3</f>
+        <v>3.8860970305248023E-2</v>
+      </c>
+      <c r="AE28">
+        <f>C28*P28*365</f>
+        <v>110813.99999999999</v>
       </c>
       <c r="AF28">
-        <f t="shared" si="4"/>
-        <v>0.99686714285714295</v>
+        <f>AE28*W28*O28*10^-3</f>
+        <v>0.34827257142857138</v>
       </c>
       <c r="AG28">
-        <f t="shared" si="5"/>
-        <v>66608.849999999991</v>
+        <f>AE28*S28</f>
+        <v>23270.939999999995</v>
       </c>
       <c r="AH28">
-        <f t="shared" si="6"/>
-        <v>0.61755919499999989</v>
+        <f>AG28*Q28*O28*10^-3</f>
+        <v>0.25598033999999997</v>
       </c>
       <c r="AI28">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AE28*R28*T28</f>
+        <v>26595.359999999997</v>
       </c>
       <c r="AJ28">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>AI28*U28*O28*10^-3</f>
+        <v>0.45971979428571424</v>
       </c>
       <c r="AM28" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AN28" s="2">
         <v>0.7</v>
@@ -3910,139 +3905,139 @@
     </row>
     <row r="29" spans="1:45">
       <c r="A29" s="2" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H29" t="str">
+        <f>VLOOKUP(G29,$AR$31:$AS$40,2,FALSE)</f>
+        <v>dry</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J29">
+        <f>VLOOKUP(A29, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.34</v>
+      </c>
+      <c r="K29">
         <f t="shared" si="0"/>
-        <v>dry</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J29">
-        <f t="shared" si="9"/>
-        <v>0.91</v>
-      </c>
-      <c r="K29">
-        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M29">
-        <f t="shared" si="10"/>
+        <f>1-N29</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N29">
-        <f t="shared" si="11"/>
+        <f>IF(L29="yes", 1, 0.95)</f>
         <v>0.95</v>
       </c>
       <c r="O29">
-        <f>$AN$4</f>
+        <f t="shared" si="1"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P29">
-        <f t="shared" si="12"/>
-        <v>13.2</v>
+        <f>VLOOKUP(A29, $AM$11:$AO$18,3,FALSE)</f>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <f t="shared" si="13"/>
-        <v>7.0000000000000001E-3</v>
+        <f>VLOOKUP(E29,$AR$10:$AS$22,2,FALSE)</f>
+        <v>1.8E-3</v>
       </c>
       <c r="R29">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f>IF(D29="yes", 1, 0)</f>
+        <v>0</v>
       </c>
       <c r="S29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="T29">
-        <f>$AQ$3</f>
+        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="U29">
-        <f>$AQ$4</f>
+        <f t="shared" si="3"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V29">
-        <f>$AN$5</f>
+        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W29">
-        <f t="shared" si="2"/>
+        <f>IF(H29="wet",$AN$6,$AN$7)</f>
         <v>2E-3</v>
       </c>
       <c r="X29">
-        <f t="shared" si="15"/>
-        <v>0.7</v>
+        <f>VLOOKUP(I29,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.74</v>
       </c>
       <c r="Y29">
-        <f t="shared" si="16"/>
-        <v>4.1053376000000034E-3</v>
+        <f>J29*K29*M29*X29*V29</f>
+        <v>1.6215116800000018E-3</v>
       </c>
       <c r="Z29">
-        <f>$AM$33</f>
+        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA29">
-        <f t="shared" si="17"/>
-        <v>5.2372378239999996E-4</v>
+        <f>J29*K29*N29*Z29*V29</f>
+        <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB29">
-        <f t="shared" si="18"/>
-        <v>34.464309152000027</v>
+        <f>C29*Y29*365</f>
+        <v>14.204442316800016</v>
       </c>
       <c r="AC29">
-        <f t="shared" si="19"/>
-        <v>4.396661153248</v>
+        <f>C29*AA29*365</f>
+        <v>1.7141306741760001</v>
       </c>
       <c r="AD29">
-        <f t="shared" si="20"/>
-        <v>3.8860970305248023E-2</v>
-      </c>
-      <c r="AE29" s="11">
-        <f t="shared" si="3"/>
-        <v>110813.99999999999</v>
+        <f>(AB29+AC29)*10^-3</f>
+        <v>1.5918572990976015E-2</v>
+      </c>
+      <c r="AE29">
+        <f>C29*P29*365</f>
+        <v>61320</v>
       </c>
       <c r="AF29">
-        <f t="shared" si="4"/>
-        <v>0.34827257142857138</v>
+        <f>AE29*W29*O29*10^-3</f>
+        <v>0.19272</v>
       </c>
       <c r="AG29">
-        <f t="shared" si="5"/>
-        <v>23270.939999999995</v>
+        <f>AE29*S29</f>
+        <v>12877.199999999999</v>
       </c>
       <c r="AH29">
-        <f t="shared" si="6"/>
-        <v>0.25598033999999997</v>
+        <f>AG29*Q29*O29*10^-3</f>
+        <v>3.6424079999999998E-2</v>
       </c>
       <c r="AI29">
-        <f t="shared" si="7"/>
-        <v>26595.359999999997</v>
+        <f>AE29*R29*T29</f>
+        <v>0</v>
       </c>
       <c r="AJ29">
-        <f t="shared" si="8"/>
-        <v>0.45971979428571424</v>
+        <f>AI29*U29*O29*10^-3</f>
+        <v>0</v>
       </c>
       <c r="AM29" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AN29" s="2">
         <v>0.74</v>
@@ -4051,140 +4046,8 @@
       <c r="AQ29" s="2"/>
     </row>
     <row r="30" spans="1:45">
-      <c r="A30" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30">
-        <v>24</v>
-      </c>
-      <c r="D30" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" t="s">
-        <v>105</v>
-      </c>
-      <c r="H30" t="str">
-        <f t="shared" si="0"/>
-        <v>dry</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J30">
-        <f t="shared" si="9"/>
-        <v>0.34</v>
-      </c>
-      <c r="K30">
-        <f>$AQ$5</f>
-        <v>0.19</v>
-      </c>
-      <c r="L30" t="s">
-        <v>58</v>
-      </c>
-      <c r="M30">
-        <f t="shared" si="10"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N30">
-        <f t="shared" si="11"/>
-        <v>0.95</v>
-      </c>
-      <c r="O30">
-        <f>$AN$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P30">
-        <f t="shared" si="12"/>
-        <v>7</v>
-      </c>
-      <c r="Q30">
-        <f t="shared" si="13"/>
-        <v>1.8E-3</v>
-      </c>
-      <c r="R30">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <f t="shared" si="1"/>
-        <v>0.21</v>
-      </c>
-      <c r="T30">
-        <f>$AQ$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U30">
-        <f>$AQ$4</f>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V30">
-        <f>$AN$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W30">
-        <f t="shared" si="2"/>
-        <v>2E-3</v>
-      </c>
-      <c r="X30">
-        <f t="shared" si="15"/>
-        <v>0.74</v>
-      </c>
-      <c r="Y30">
-        <f t="shared" si="16"/>
-        <v>1.6215116800000018E-3</v>
-      </c>
-      <c r="Z30">
-        <f>$AM$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA30">
-        <f t="shared" si="17"/>
-        <v>1.9567701760000002E-4</v>
-      </c>
-      <c r="AB30">
-        <f t="shared" si="18"/>
-        <v>14.204442316800016</v>
-      </c>
-      <c r="AC30">
-        <f t="shared" si="19"/>
-        <v>1.7141306741760001</v>
-      </c>
-      <c r="AD30">
-        <f t="shared" si="20"/>
-        <v>1.5918572990976015E-2</v>
-      </c>
-      <c r="AE30" s="11">
-        <f t="shared" si="3"/>
-        <v>61320</v>
-      </c>
-      <c r="AF30">
-        <f t="shared" si="4"/>
-        <v>0.19272</v>
-      </c>
-      <c r="AG30">
-        <f t="shared" si="5"/>
-        <v>12877.199999999999</v>
-      </c>
-      <c r="AH30">
-        <f t="shared" si="6"/>
-        <v>3.6424079999999998E-2</v>
-      </c>
-      <c r="AI30">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ30">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
       <c r="AM30" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AN30" s="2">
         <v>0.76</v>
@@ -4196,22 +4059,22 @@
       <c r="E31" s="2"/>
       <c r="I31" s="2"/>
       <c r="AR31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AS31" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:45">
       <c r="E32" s="2"/>
       <c r="AM32" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AR32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AS32" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:45">
@@ -4220,58 +4083,58 @@
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AR33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AS33" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:45">
       <c r="E34" s="2"/>
       <c r="AR34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AS34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:45">
       <c r="E35" s="2"/>
       <c r="AM35" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AR35" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AS35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:45">
       <c r="E36" s="2"/>
       <c r="AM36" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AR36" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AS36" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:45">
       <c r="E37" s="2"/>
       <c r="AM37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AN37">
         <v>0.66</v>
       </c>
       <c r="AR37" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AS37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:45">
@@ -4283,10 +4146,10 @@
         <v>0.68</v>
       </c>
       <c r="AR38" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AS38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:45">
@@ -4297,10 +4160,10 @@
         <v>0.7</v>
       </c>
       <c r="AR39" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AS39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:45">
@@ -4311,10 +4174,10 @@
         <v>0.71</v>
       </c>
       <c r="AR40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AS40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:45" ht="17">
@@ -4328,27 +4191,27 @@
         <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J41">
         <f>VLOOKUP(A41, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K41">
-        <f>$AQ$5</f>
+        <f t="shared" ref="K41:K60" si="27">$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L41" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M41">
         <f>1-N41</f>
@@ -4359,7 +4222,7 @@
         <v>0.95</v>
       </c>
       <c r="O41">
-        <f>$AN$4</f>
+        <f t="shared" ref="O41:O60" si="28">$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P41">
@@ -4375,15 +4238,15 @@
         <v>1</v>
       </c>
       <c r="T41">
-        <f>$AQ$3</f>
+        <f t="shared" ref="T41:T60" si="29">$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U41">
-        <f>$AQ$4</f>
+        <f t="shared" ref="U41:U60" si="30">$AQ$4</f>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V41">
-        <f>$AN$5</f>
+        <f t="shared" ref="V41:V60" si="31">$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="X41">
@@ -4395,7 +4258,7 @@
         <v>1.1612240640000012E-2</v>
       </c>
       <c r="Z41">
-        <f>$AM$33</f>
+        <f t="shared" ref="Z41:Z60" si="32">$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA41">
@@ -4432,27 +4295,27 @@
         <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F42">
         <v>11</v>
       </c>
       <c r="I42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J42">
         <f>VLOOKUP(A42, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K42">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L42" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M42">
         <f>1-N42</f>
@@ -4463,7 +4326,7 @@
         <v>0.95</v>
       </c>
       <c r="O42">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P42">
@@ -4479,19 +4342,19 @@
         <v>0</v>
       </c>
       <c r="T42">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U42">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V42">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X42">
-        <f t="shared" ref="X42:X60" si="21">VLOOKUP(F42, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" ref="X42:X60" si="33">VLOOKUP(F42, $AM$37:$AN$55, 2, FALSE)</f>
         <v>0.68</v>
       </c>
       <c r="Y42">
@@ -4499,7 +4362,7 @@
         <v>1.1964126720000011E-2</v>
       </c>
       <c r="Z42">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA42">
@@ -4536,90 +4399,90 @@
         <v>7</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F43">
         <v>12</v>
       </c>
       <c r="I43" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J43">
-        <f t="shared" ref="J43:J60" si="22">VLOOKUP(A43, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" ref="J43:J60" si="34">VLOOKUP(A43, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K43">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M43">
-        <f t="shared" ref="M43:M60" si="23">1-N43</f>
+        <f t="shared" ref="M43:M60" si="35">1-N43</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N43">
-        <f t="shared" ref="N43:N60" si="24">IF(L43="yes", 1, 0.95)</f>
+        <f t="shared" ref="N43:N60" si="36">IF(L43="yes", 1, 0.95)</f>
         <v>0.95</v>
       </c>
       <c r="O43">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P43">
-        <f t="shared" ref="P43:P60" si="25">VLOOKUP(A43, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" ref="P43:P60" si="37">VLOOKUP(A43, $AM$11:$AO$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q43">
-        <f t="shared" ref="Q43:Q60" si="26">VLOOKUP(E43,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" ref="Q43:Q60" si="38">VLOOKUP(E43,$AR$10:$AS$22,2,FALSE)</f>
         <v>1.8E-3</v>
       </c>
       <c r="R43">
-        <f t="shared" ref="R43:R60" si="27">IF(D43="yes", 1, 0)</f>
+        <f t="shared" ref="R43:R60" si="39">IF(D43="yes", 1, 0)</f>
         <v>1</v>
       </c>
       <c r="T43">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U43">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V43">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X43">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>0.7</v>
       </c>
       <c r="Y43">
-        <f t="shared" ref="Y43:Y60" si="28">J43*K43*M43*X43*V43</f>
+        <f t="shared" ref="Y43:Y60" si="40">J43*K43*M43*X43*V43</f>
         <v>1.231601280000001E-2</v>
       </c>
       <c r="Z43">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA43">
-        <f t="shared" ref="AA43:AA60" si="29">J43*K43*N43*Z43*V43</f>
+        <f t="shared" ref="AA43:AA60" si="41">J43*K43*N43*Z43*V43</f>
         <v>1.5711713472E-3</v>
       </c>
       <c r="AB43">
-        <f t="shared" ref="AB43:AB60" si="30">C43*Y43*365</f>
+        <f t="shared" ref="AB43:AB60" si="42">C43*Y43*365</f>
         <v>31.467412704000026</v>
       </c>
       <c r="AC43">
-        <f t="shared" ref="AC43:AC60" si="31">C43*AA43*365</f>
+        <f t="shared" ref="AC43:AC60" si="43">C43*AA43*365</f>
         <v>4.0143427920960004</v>
       </c>
       <c r="AD43">
-        <f t="shared" ref="AD43:AD60" si="32">(AB43+AC43)*10^-3</f>
+        <f t="shared" ref="AD43:AD60" si="44">(AB43+AC43)*10^-3</f>
         <v>3.5481755496096029E-2</v>
       </c>
       <c r="AM43">
@@ -4640,90 +4503,90 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F44">
         <v>13</v>
       </c>
       <c r="I44" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J44">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>2.73</v>
       </c>
       <c r="K44">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M44">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>0.95</v>
       </c>
       <c r="O44">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P44">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>39.5</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="R44">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T44">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U44">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V44">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X44">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>0.71</v>
       </c>
       <c r="Y44">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>1.2491955840000011E-2</v>
       </c>
       <c r="Z44">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>1.5711713472E-3</v>
       </c>
       <c r="AB44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>36.476511052800035</v>
       </c>
       <c r="AC44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>4.5878203338240002</v>
       </c>
       <c r="AD44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>4.1064331386624034E-2</v>
       </c>
       <c r="AM44">
@@ -4735,7 +4598,7 @@
     </row>
     <row r="45" spans="1:45" ht="17">
       <c r="A45" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>8</v>
@@ -4744,90 +4607,90 @@
         <v>9</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F45">
         <v>14</v>
       </c>
       <c r="I45" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J45">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>0.34</v>
       </c>
       <c r="K45">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L45" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M45">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N45">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>0.95</v>
       </c>
       <c r="O45">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P45">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>7</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="R45">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="T45">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U45">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V45">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X45">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>0.73</v>
       </c>
       <c r="Y45">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>1.5995993600000015E-3</v>
       </c>
       <c r="Z45">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB45">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>5.254683897600005</v>
       </c>
       <c r="AC45">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>0.64279900281600011</v>
       </c>
       <c r="AD45">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>5.8974829004160047E-3</v>
       </c>
       <c r="AM45">
@@ -4839,7 +4702,7 @@
     </row>
     <row r="46" spans="1:45" ht="17">
       <c r="A46" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>9</v>
@@ -4848,90 +4711,90 @@
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F46">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>0.34</v>
       </c>
       <c r="K46">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>0.95</v>
       </c>
       <c r="O46">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>7</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>1.9900000000000001E-2</v>
       </c>
       <c r="R46">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T46">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U46">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V46">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>0.74</v>
       </c>
       <c r="Y46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>1.6215116800000018E-3</v>
       </c>
       <c r="Z46">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA46">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>5.9185176320000075</v>
       </c>
       <c r="AC46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>0.71422111424000012</v>
       </c>
       <c r="AD46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>6.6327387462400073E-3</v>
       </c>
       <c r="AM46">
@@ -4943,99 +4806,99 @@
     </row>
     <row r="47" spans="1:45" ht="17">
       <c r="A47" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="C47">
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F47">
         <v>16</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>0.34</v>
       </c>
       <c r="K47">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L47" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M47">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N47">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>0.95</v>
       </c>
       <c r="O47">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P47">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>7</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>5.3E-3</v>
       </c>
       <c r="R47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="T47">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U47">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V47">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>0.75</v>
       </c>
       <c r="Y47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>1.6434240000000016E-3</v>
       </c>
       <c r="Z47">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA47">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>6.5983473600000062</v>
       </c>
       <c r="AC47">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>0.78564322566400013</v>
       </c>
       <c r="AD47">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>7.383990585664006E-3</v>
       </c>
       <c r="AM47">
@@ -5047,100 +4910,100 @@
     </row>
     <row r="48" spans="1:45" ht="17">
       <c r="A48" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C48">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F48">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J48">
-        <f t="shared" si="22"/>
+        <f>VLOOKUP(A48, $AM$11:$AN$18,2,FALSE)</f>
         <v>0.34</v>
       </c>
       <c r="K48">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M48">
-        <f t="shared" si="23"/>
+        <f>1-N48</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N48">
-        <f t="shared" si="24"/>
+        <f>IF(L48="yes", 1, 0.95)</f>
         <v>0.95</v>
       </c>
       <c r="O48">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P48">
-        <f t="shared" si="25"/>
+        <f>VLOOKUP(A48, $AM$11:$AO$18,3,FALSE)</f>
         <v>7</v>
       </c>
       <c r="Q48">
-        <f t="shared" si="26"/>
-        <v>6.4000000000000003E-3</v>
+        <f>VLOOKUP(E48,$AR$10:$AS$22,2,FALSE)</f>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="R48">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>IF(D48="yes", 1, 0)</f>
+        <v>1</v>
       </c>
       <c r="T48">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U48">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V48">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X48">
-        <f t="shared" si="21"/>
-        <v>0.76</v>
+        <f>VLOOKUP(F48, $AM$37:$AN$55, 2, FALSE)</f>
+        <v>0.77</v>
       </c>
       <c r="Y48">
-        <f t="shared" si="28"/>
-        <v>1.6653363200000019E-3</v>
+        <f>J48*K48*M48*X48*V48</f>
+        <v>1.6872486400000017E-3</v>
       </c>
       <c r="Z48">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA48">
-        <f t="shared" si="29"/>
+        <f>J48*K48*N48*Z48*V48</f>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB48">
-        <f t="shared" si="30"/>
-        <v>7.2941730816000083</v>
+        <f>C48*Y48*365</f>
+        <v>8.0059947968000085</v>
       </c>
       <c r="AC48">
-        <f t="shared" si="31"/>
-        <v>0.85706533708800003</v>
+        <f>C48*AA48*365</f>
+        <v>0.92848744851200005</v>
       </c>
       <c r="AD48">
-        <f t="shared" si="32"/>
-        <v>8.1512384186880078E-3</v>
+        <f>(AB48+AC48)*10^-3</f>
+        <v>8.9344822453120091E-3</v>
       </c>
       <c r="AM48">
         <v>21</v>
@@ -5151,100 +5014,100 @@
     </row>
     <row r="49" spans="1:40" ht="17">
       <c r="A49" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C49">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F49">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J49">
-        <f t="shared" si="22"/>
+        <f>VLOOKUP(A49, $AM$11:$AN$18,2,FALSE)</f>
         <v>0.34</v>
       </c>
       <c r="K49">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L49" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M49">
-        <f t="shared" si="23"/>
+        <f>1-N49</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N49">
-        <f t="shared" si="24"/>
+        <f>IF(L49="yes", 1, 0.95)</f>
         <v>0.95</v>
       </c>
       <c r="O49">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P49">
-        <f t="shared" si="25"/>
+        <f>VLOOKUP(A49, $AM$11:$AO$18,3,FALSE)</f>
         <v>7</v>
       </c>
       <c r="Q49">
-        <f t="shared" si="26"/>
-        <v>2.5999999999999999E-3</v>
+        <f>VLOOKUP(E49,$AR$10:$AS$22,2,FALSE)</f>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="R49">
-        <f t="shared" si="27"/>
-        <v>1</v>
+        <f>IF(D49="yes", 1, 0)</f>
+        <v>0</v>
       </c>
       <c r="T49">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U49">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V49">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X49">
-        <f t="shared" si="21"/>
+        <f>VLOOKUP(F49, $AM$37:$AN$55, 2, FALSE)</f>
         <v>0.77</v>
       </c>
       <c r="Y49">
-        <f t="shared" si="28"/>
+        <f>J49*K49*M49*X49*V49</f>
         <v>1.6872486400000017E-3</v>
       </c>
       <c r="Z49">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA49">
-        <f t="shared" si="29"/>
+        <f>J49*K49*N49*Z49*V49</f>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB49">
-        <f t="shared" si="30"/>
-        <v>8.0059947968000085</v>
+        <f>C49*Y49*365</f>
+        <v>8.6218405504000089</v>
       </c>
       <c r="AC49">
-        <f t="shared" si="31"/>
-        <v>0.92848744851200005</v>
+        <f>C49*AA49*365</f>
+        <v>0.99990955993600006</v>
       </c>
       <c r="AD49">
-        <f t="shared" si="32"/>
-        <v>8.9344822453120091E-3</v>
+        <f>(AB49+AC49)*10^-3</f>
+        <v>9.6217501103360095E-3</v>
       </c>
       <c r="AM49">
         <v>22</v>
@@ -5255,100 +5118,100 @@
     </row>
     <row r="50" spans="1:40" ht="17">
       <c r="A50" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C50">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F50">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J50">
-        <f t="shared" si="22"/>
+        <f>VLOOKUP(A50, $AM$11:$AN$18,2,FALSE)</f>
         <v>0.34</v>
       </c>
       <c r="K50">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L50" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M50">
-        <f t="shared" si="23"/>
-        <v>5.0000000000000044E-2</v>
+        <f>1-N50</f>
+        <v>0</v>
       </c>
       <c r="N50">
-        <f t="shared" si="24"/>
-        <v>0.95</v>
+        <f>IF(L50="yes", 1, 0.95)</f>
+        <v>1</v>
       </c>
       <c r="O50">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P50">
-        <f t="shared" si="25"/>
+        <f>VLOOKUP(A50, $AM$11:$AO$18,3,FALSE)</f>
         <v>7</v>
       </c>
       <c r="Q50">
-        <f t="shared" si="26"/>
-        <v>3.0000000000000001E-3</v>
+        <f>VLOOKUP(E50,$AR$10:$AS$22,2,FALSE)</f>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="R50">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>IF(D50="yes", 1, 0)</f>
+        <v>1</v>
       </c>
       <c r="T50">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U50">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V50">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X50">
-        <f t="shared" si="21"/>
-        <v>0.77</v>
+        <f>VLOOKUP(F50, $AM$37:$AN$55, 2, FALSE)</f>
+        <v>0.78</v>
       </c>
       <c r="Y50">
-        <f t="shared" si="28"/>
-        <v>1.6872486400000017E-3</v>
+        <f>J50*K50*M50*X50*V50</f>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA50">
-        <f t="shared" si="29"/>
-        <v>1.9567701760000002E-4</v>
+        <f>J50*K50*N50*Z50*V50</f>
+        <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB50">
-        <f t="shared" si="30"/>
-        <v>8.6218405504000089</v>
+        <f>C50*Y50*365</f>
+        <v>0</v>
       </c>
       <c r="AC50">
-        <f t="shared" si="31"/>
-        <v>0.99990955993600006</v>
+        <f>C50*AA50*365</f>
+        <v>1.1277175488000002</v>
       </c>
       <c r="AD50">
-        <f t="shared" si="32"/>
-        <v>9.6217501103360095E-3</v>
+        <f>(AB50+AC50)*10^-3</f>
+        <v>1.1277175488000003E-3</v>
       </c>
       <c r="AM50">
         <v>23</v>
@@ -5359,100 +5222,100 @@
     </row>
     <row r="51" spans="1:40" ht="17">
       <c r="A51" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F51">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J51">
-        <f t="shared" si="22"/>
-        <v>0.34</v>
+        <f>VLOOKUP(A51, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.91</v>
       </c>
       <c r="K51">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L51" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M51">
-        <f t="shared" si="23"/>
+        <f>1-N51</f>
         <v>0</v>
       </c>
       <c r="N51">
-        <f t="shared" si="24"/>
+        <f>IF(L51="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O51">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P51">
-        <f t="shared" si="25"/>
-        <v>7</v>
+        <f>VLOOKUP(A51, $AM$11:$AO$18,3,FALSE)</f>
+        <v>13.2</v>
       </c>
       <c r="Q51">
-        <f t="shared" si="26"/>
-        <v>5.0000000000000001E-3</v>
+        <f>VLOOKUP(E51,$AR$10:$AS$22,2,FALSE)</f>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="R51">
-        <f t="shared" si="27"/>
-        <v>1</v>
+        <f>IF(D51="yes", 1, 0)</f>
+        <v>0</v>
       </c>
       <c r="T51">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U51">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V51">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X51">
-        <f t="shared" si="21"/>
+        <f>VLOOKUP(F51, $AM$37:$AN$55, 2, FALSE)</f>
         <v>0.78</v>
       </c>
       <c r="Y51">
-        <f t="shared" si="28"/>
+        <f>J51*K51*M51*X51*V51</f>
         <v>0</v>
       </c>
       <c r="Z51">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA51">
-        <f t="shared" si="29"/>
-        <v>2.0597580800000003E-4</v>
+        <f>J51*K51*N51*Z51*V51</f>
+        <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB51">
-        <f t="shared" si="30"/>
+        <f>C51*Y51*365</f>
         <v>0</v>
       </c>
       <c r="AC51">
-        <f t="shared" si="31"/>
-        <v>1.1277175488000002</v>
+        <f>C51*AA51*365</f>
+        <v>3.21952304128</v>
       </c>
       <c r="AD51">
-        <f t="shared" si="32"/>
-        <v>1.1277175488000003E-3</v>
+        <f>(AB51+AC51)*10^-3</f>
+        <v>3.21952304128E-3</v>
       </c>
       <c r="AM51">
         <v>24</v>
@@ -5463,100 +5326,100 @@
     </row>
     <row r="52" spans="1:40" ht="17">
       <c r="A52" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C52">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F52">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J52">
-        <f t="shared" si="22"/>
+        <f>VLOOKUP(A52, $AM$11:$AN$18,2,FALSE)</f>
         <v>0.91</v>
       </c>
       <c r="K52">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L52" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M52">
-        <f t="shared" si="23"/>
+        <f>1-N52</f>
         <v>0</v>
       </c>
       <c r="N52">
-        <f t="shared" si="24"/>
+        <f>IF(L52="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O52">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P52">
-        <f t="shared" si="25"/>
+        <f>VLOOKUP(A52, $AM$11:$AO$18,3,FALSE)</f>
         <v>13.2</v>
       </c>
       <c r="Q52">
-        <f t="shared" si="26"/>
-        <v>2.5999999999999999E-3</v>
+        <f>VLOOKUP(E52,$AR$10:$AS$22,2,FALSE)</f>
+        <v>1.8E-3</v>
       </c>
       <c r="R52">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>IF(D52="yes", 1, 0)</f>
+        <v>1</v>
       </c>
       <c r="T52">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U52">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V52">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X52">
-        <f t="shared" si="21"/>
+        <f>VLOOKUP(F52, $AM$37:$AN$55, 2, FALSE)</f>
         <v>0.78</v>
       </c>
       <c r="Y52">
-        <f t="shared" si="28"/>
+        <f>J52*K52*M52*X52*V52</f>
         <v>0</v>
       </c>
       <c r="Z52">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA52">
-        <f t="shared" si="29"/>
+        <f>J52*K52*N52*Z52*V52</f>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB52">
-        <f t="shared" si="30"/>
+        <f>C52*Y52*365</f>
         <v>0</v>
       </c>
       <c r="AC52">
-        <f t="shared" si="31"/>
-        <v>3.21952304128</v>
+        <f>C52*AA52*365</f>
+        <v>3.4207432313599999</v>
       </c>
       <c r="AD52">
-        <f t="shared" si="32"/>
-        <v>3.21952304128E-3</v>
+        <f>(AB52+AC52)*10^-3</f>
+        <v>3.4207432313600001E-3</v>
       </c>
       <c r="AM52">
         <v>25</v>
@@ -5567,100 +5430,100 @@
     </row>
     <row r="53" spans="1:40" ht="17">
       <c r="A53" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C53">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F53">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="J53">
-        <f t="shared" si="22"/>
+        <f>VLOOKUP(A53, $AM$11:$AN$18,2,FALSE)</f>
         <v>0.91</v>
       </c>
       <c r="K53">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M53">
-        <f t="shared" si="23"/>
+        <f>1-N53</f>
         <v>0</v>
       </c>
       <c r="N53">
-        <f t="shared" si="24"/>
+        <f>IF(L53="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O53">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P53">
-        <f t="shared" si="25"/>
+        <f>VLOOKUP(A53, $AM$11:$AO$18,3,FALSE)</f>
         <v>13.2</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="26"/>
+        <f>VLOOKUP(E53,$AR$10:$AS$22,2,FALSE)</f>
         <v>1.8E-3</v>
       </c>
       <c r="R53">
-        <f t="shared" si="27"/>
-        <v>1</v>
+        <f>IF(D53="yes", 1, 0)</f>
+        <v>0</v>
       </c>
       <c r="T53">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U53">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V53">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X53">
-        <f t="shared" si="21"/>
-        <v>0.78</v>
+        <f>VLOOKUP(F53, $AM$37:$AN$55, 2, FALSE)</f>
+        <v>0.79</v>
       </c>
       <c r="Y53">
-        <f t="shared" si="28"/>
+        <f>J53*K53*M53*X53*V53</f>
         <v>0</v>
       </c>
       <c r="Z53">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA53">
-        <f t="shared" si="29"/>
+        <f>J53*K53*N53*Z53*V53</f>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB53">
-        <f t="shared" si="30"/>
+        <f>C53*Y53*365</f>
         <v>0</v>
       </c>
       <c r="AC53">
-        <f t="shared" si="31"/>
-        <v>3.4207432313599999</v>
+        <f>C53*AA53*365</f>
+        <v>3.6219634214399998</v>
       </c>
       <c r="AD53">
-        <f t="shared" si="32"/>
-        <v>3.4207432313600001E-3</v>
+        <f>(AB53+AC53)*10^-3</f>
+        <v>3.6219634214399998E-3</v>
       </c>
       <c r="AM53">
         <v>26</v>
@@ -5671,100 +5534,100 @@
     </row>
     <row r="54" spans="1:40" ht="17">
       <c r="A54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54">
+        <v>19</v>
+      </c>
+      <c r="D54" t="s">
+        <v>55</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F54">
         <v>24</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54">
-        <v>18</v>
-      </c>
-      <c r="D54" t="s">
-        <v>58</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F54">
-        <v>23</v>
-      </c>
       <c r="I54" s="2" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="J54">
-        <f t="shared" si="22"/>
+        <f>VLOOKUP(A54, $AM$11:$AN$18,2,FALSE)</f>
         <v>0.91</v>
       </c>
       <c r="K54">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L54" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M54">
-        <f t="shared" si="23"/>
+        <f>1-N54</f>
         <v>0</v>
       </c>
       <c r="N54">
-        <f t="shared" si="24"/>
+        <f>IF(L54="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O54">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P54">
-        <f t="shared" si="25"/>
+        <f>VLOOKUP(A54, $AM$11:$AO$18,3,FALSE)</f>
         <v>13.2</v>
       </c>
       <c r="Q54">
-        <f t="shared" si="26"/>
-        <v>1.8E-3</v>
+        <f>VLOOKUP(E54,$AR$10:$AS$22,2,FALSE)</f>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="R54">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>IF(D54="yes", 1, 0)</f>
+        <v>1</v>
       </c>
       <c r="T54">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U54">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V54">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X54">
-        <f t="shared" si="21"/>
+        <f>VLOOKUP(F54, $AM$37:$AN$55, 2, FALSE)</f>
         <v>0.79</v>
       </c>
       <c r="Y54">
-        <f t="shared" si="28"/>
+        <f>J54*K54*M54*X54*V54</f>
         <v>0</v>
       </c>
       <c r="Z54">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA54">
-        <f t="shared" si="29"/>
+        <f>J54*K54*N54*Z54*V54</f>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB54">
-        <f t="shared" si="30"/>
+        <f>C54*Y54*365</f>
         <v>0</v>
       </c>
       <c r="AC54">
-        <f t="shared" si="31"/>
-        <v>3.6219634214399998</v>
+        <f>C54*AA54*365</f>
+        <v>3.8231836115200006</v>
       </c>
       <c r="AD54">
-        <f t="shared" si="32"/>
-        <v>3.6219634214399998E-3</v>
+        <f>(AB54+AC54)*10^-3</f>
+        <v>3.8231836115200008E-3</v>
       </c>
       <c r="AM54">
         <v>27</v>
@@ -5773,105 +5636,105 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="55" spans="1:40" ht="17">
-      <c r="A55" s="3" t="s">
-        <v>24</v>
+    <row r="55" spans="1:40">
+      <c r="A55" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C55">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F55">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J55">
-        <f t="shared" si="22"/>
-        <v>0.91</v>
+        <f>VLOOKUP(A55, $AM$11:$AN$18,2,FALSE)</f>
+        <v>2.73</v>
       </c>
       <c r="K55">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L55" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M55">
-        <f t="shared" si="23"/>
+        <f>1-N55</f>
         <v>0</v>
       </c>
       <c r="N55">
-        <f t="shared" si="24"/>
+        <f>IF(L55="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O55">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P55">
-        <f t="shared" si="25"/>
-        <v>13.2</v>
+        <f>VLOOKUP(A55, $AM$11:$AO$18,3,FALSE)</f>
+        <v>39.5</v>
       </c>
       <c r="Q55">
-        <f t="shared" si="26"/>
-        <v>2.8999999999999998E-3</v>
+        <f>VLOOKUP(E55,$AR$10:$AS$22,2,FALSE)</f>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="R55">
-        <f t="shared" si="27"/>
-        <v>1</v>
+        <f>IF(D55="yes", 1, 0)</f>
+        <v>0</v>
       </c>
       <c r="T55">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U55">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V55">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X55">
-        <f t="shared" si="21"/>
+        <f>VLOOKUP(F55, $AM$37:$AN$55, 2, FALSE)</f>
         <v>0.79</v>
       </c>
       <c r="Y55">
-        <f t="shared" si="28"/>
+        <f>J55*K55*M55*X55*V55</f>
         <v>0</v>
       </c>
       <c r="Z55">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA55">
-        <f t="shared" si="29"/>
-        <v>5.5128819200000003E-4</v>
+        <f>J55*K55*N55*Z55*V55</f>
+        <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB55">
-        <f t="shared" si="30"/>
+        <f>C55*Y55*365</f>
         <v>0</v>
       </c>
       <c r="AC55">
-        <f t="shared" si="31"/>
-        <v>3.8231836115200006</v>
+        <f>C55*AA55*365</f>
+        <v>12.0732114048</v>
       </c>
       <c r="AD55">
-        <f t="shared" si="32"/>
-        <v>3.8231836115200008E-3</v>
+        <f>(AB55+AC55)*10^-3</f>
+        <v>1.2073211404800001E-2</v>
       </c>
       <c r="AM55" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AN55">
         <v>0.8</v>
@@ -5879,491 +5742,393 @@
     </row>
     <row r="56" spans="1:40">
       <c r="A56" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C56">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F56">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J56">
-        <f t="shared" si="22"/>
-        <v>2.73</v>
+        <f>VLOOKUP(A56, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.34</v>
       </c>
       <c r="K56">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L56" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M56">
-        <f t="shared" si="23"/>
+        <f>1-N56</f>
         <v>0</v>
       </c>
       <c r="N56">
-        <f t="shared" si="24"/>
+        <f>IF(L56="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O56">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P56">
-        <f t="shared" si="25"/>
-        <v>39.5</v>
+        <f>VLOOKUP(A56, $AM$11:$AO$18,3,FALSE)</f>
+        <v>7</v>
       </c>
       <c r="Q56">
-        <f t="shared" si="26"/>
-        <v>8.0000000000000002E-3</v>
+        <f>VLOOKUP(E56,$AR$10:$AS$22,2,FALSE)</f>
+        <v>1.9900000000000001E-2</v>
       </c>
       <c r="R56">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>IF(D56="yes", 1, 0)</f>
+        <v>1</v>
       </c>
       <c r="T56">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U56">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V56">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X56">
-        <f t="shared" si="21"/>
+        <f>VLOOKUP(F56, $AM$37:$AN$55, 2, FALSE)</f>
         <v>0.79</v>
       </c>
       <c r="Y56">
-        <f t="shared" si="28"/>
+        <f>J56*K56*M56*X56*V56</f>
         <v>0</v>
       </c>
       <c r="Z56">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA56">
-        <f t="shared" si="29"/>
-        <v>1.6538645760000002E-3</v>
+        <f>J56*K56*N56*Z56*V56</f>
+        <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB56">
-        <f t="shared" si="30"/>
+        <f>C56*Y56*365</f>
         <v>0</v>
       </c>
       <c r="AC56">
-        <f t="shared" si="31"/>
-        <v>12.0732114048</v>
+        <f>C56*AA56*365</f>
+        <v>1.57880456832</v>
       </c>
       <c r="AD56">
-        <f t="shared" si="32"/>
-        <v>1.2073211404800001E-2</v>
+        <f>(AB56+AC56)*10^-3</f>
+        <v>1.5788045683200001E-3</v>
       </c>
     </row>
     <row r="57" spans="1:40">
       <c r="A57" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C57">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F57">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J57">
-        <f t="shared" si="22"/>
-        <v>0.34</v>
+        <f>VLOOKUP(A57, $AM$11:$AN$18,2,FALSE)</f>
+        <v>2.73</v>
       </c>
       <c r="K57">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L57" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M57">
-        <f t="shared" si="23"/>
+        <f>1-N57</f>
         <v>0</v>
       </c>
       <c r="N57">
-        <f t="shared" si="24"/>
+        <f>IF(L57="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O57">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P57">
-        <f t="shared" si="25"/>
-        <v>7</v>
+        <f>VLOOKUP(A57, $AM$11:$AO$18,3,FALSE)</f>
+        <v>39.5</v>
       </c>
       <c r="Q57">
-        <f t="shared" si="26"/>
-        <v>1.9900000000000001E-2</v>
+        <f>VLOOKUP(E57,$AR$10:$AS$22,2,FALSE)</f>
+        <v>5.3E-3</v>
       </c>
       <c r="R57">
-        <f t="shared" si="27"/>
-        <v>1</v>
+        <f>IF(D57="yes", 1, 0)</f>
+        <v>0</v>
       </c>
       <c r="T57">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U57">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V57">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X57">
-        <f t="shared" si="21"/>
-        <v>0.79</v>
+        <f>VLOOKUP(F57, $AM$37:$AN$55, 2, FALSE)</f>
+        <v>0.8</v>
       </c>
       <c r="Y57">
-        <f t="shared" si="28"/>
+        <f>J57*K57*M57*X57*V57</f>
         <v>0</v>
       </c>
       <c r="Z57">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA57">
-        <f t="shared" si="29"/>
-        <v>2.0597580800000003E-4</v>
+        <f>J57*K57*N57*Z57*V57</f>
+        <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB57">
-        <f t="shared" si="30"/>
+        <f>C57*Y57*365</f>
         <v>0</v>
       </c>
       <c r="AC57">
-        <f t="shared" si="31"/>
-        <v>1.57880456832</v>
+        <f>C57*AA57*365</f>
+        <v>13.28053254528</v>
       </c>
       <c r="AD57">
-        <f t="shared" si="32"/>
-        <v>1.5788045683200001E-3</v>
+        <f>(AB57+AC57)*10^-3</f>
+        <v>1.3280532545279999E-2</v>
       </c>
     </row>
     <row r="58" spans="1:40">
       <c r="A58" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C58">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D58" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F58">
-        <v>27</v>
+        <v>79</v>
+      </c>
+      <c r="F58" t="s">
+        <v>91</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J58">
-        <f t="shared" si="22"/>
-        <v>2.73</v>
+        <f>VLOOKUP(A58, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.91</v>
       </c>
       <c r="K58">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L58" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M58">
-        <f t="shared" si="23"/>
+        <f>1-N58</f>
         <v>0</v>
       </c>
       <c r="N58">
-        <f t="shared" si="24"/>
+        <f>IF(L58="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O58">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P58">
-        <f t="shared" si="25"/>
-        <v>39.5</v>
+        <f>VLOOKUP(A58, $AM$11:$AO$18,3,FALSE)</f>
+        <v>13.2</v>
       </c>
       <c r="Q58">
-        <f t="shared" si="26"/>
-        <v>5.3E-3</v>
+        <f>VLOOKUP(E58,$AR$10:$AS$22,2,FALSE)</f>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="R58">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>IF(D58="yes", 1, 0)</f>
+        <v>1</v>
       </c>
       <c r="T58">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U58">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V58">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X58">
-        <f t="shared" si="21"/>
+        <f>VLOOKUP(F58, $AM$37:$AN$55, 2, FALSE)</f>
         <v>0.8</v>
       </c>
       <c r="Y58">
-        <f t="shared" si="28"/>
+        <f>J58*K58*M58*X58*V58</f>
         <v>0</v>
       </c>
       <c r="Z58">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA58">
-        <f t="shared" si="29"/>
-        <v>1.6538645760000002E-3</v>
+        <f>J58*K58*N58*Z58*V58</f>
+        <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB58">
-        <f t="shared" si="30"/>
+        <f>C58*Y58*365</f>
         <v>0</v>
       </c>
       <c r="AC58">
-        <f t="shared" si="31"/>
-        <v>13.28053254528</v>
+        <f>C58*AA58*365</f>
+        <v>4.6280643718399999</v>
       </c>
       <c r="AD58">
-        <f t="shared" si="32"/>
-        <v>1.3280532545279999E-2</v>
+        <f>(AB58+AC58)*10^-3</f>
+        <v>4.6280643718400001E-3</v>
       </c>
     </row>
     <row r="59" spans="1:40">
       <c r="A59" s="2" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C59">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D59" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F59" t="s">
-        <v>93</v>
+        <v>80</v>
+      </c>
+      <c r="F59">
+        <v>20</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J59">
-        <f t="shared" si="22"/>
-        <v>0.91</v>
+        <f>VLOOKUP(A59, $AM$11:$AN$18,2,FALSE)</f>
+        <v>0.34</v>
       </c>
       <c r="K59">
-        <f>$AQ$5</f>
+        <f t="shared" si="27"/>
         <v>0.19</v>
       </c>
       <c r="L59" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M59">
-        <f t="shared" si="23"/>
+        <f>1-N59</f>
         <v>0</v>
       </c>
       <c r="N59">
-        <f t="shared" si="24"/>
+        <f>IF(L59="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O59">
-        <f>$AN$4</f>
+        <f t="shared" si="28"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P59">
-        <f t="shared" si="25"/>
-        <v>13.2</v>
+        <f>VLOOKUP(A59, $AM$11:$AO$18,3,FALSE)</f>
+        <v>7</v>
       </c>
       <c r="Q59">
-        <f t="shared" si="26"/>
-        <v>6.4000000000000003E-3</v>
+        <f>VLOOKUP(E59,$AR$10:$AS$22,2,FALSE)</f>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="R59">
-        <f t="shared" si="27"/>
-        <v>1</v>
+        <f>IF(D59="yes", 1, 0)</f>
+        <v>0</v>
       </c>
       <c r="T59">
-        <f>$AQ$3</f>
+        <f t="shared" si="29"/>
         <v>0.24</v>
       </c>
       <c r="U59">
-        <f>$AQ$4</f>
+        <f t="shared" si="30"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V59">
-        <f>$AN$5</f>
+        <f t="shared" si="31"/>
         <v>0.6784</v>
       </c>
       <c r="X59">
-        <f t="shared" si="21"/>
-        <v>0.8</v>
+        <f>VLOOKUP(F59, $AM$37:$AN$55, 2, FALSE)</f>
+        <v>0.78</v>
       </c>
       <c r="Y59">
-        <f t="shared" si="28"/>
+        <f>J59*K59*M59*X59*V59</f>
         <v>0</v>
       </c>
       <c r="Z59">
-        <f>$AM$33</f>
+        <f t="shared" si="32"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA59">
-        <f t="shared" si="29"/>
-        <v>5.5128819200000003E-4</v>
+        <f>J59*K59*N59*Z59*V59</f>
+        <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB59">
-        <f t="shared" si="30"/>
+        <f>C59*Y59*365</f>
         <v>0</v>
       </c>
       <c r="AC59">
-        <f t="shared" si="31"/>
-        <v>4.6280643718399999</v>
+        <f>C59*AA59*365</f>
+        <v>1.8043480780800005</v>
       </c>
       <c r="AD59">
-        <f t="shared" si="32"/>
-        <v>4.6280643718400001E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:40">
-      <c r="A60" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60">
-        <v>24</v>
-      </c>
-      <c r="D60" t="s">
-        <v>58</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F60">
-        <v>20</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J60">
-        <f t="shared" si="22"/>
-        <v>0.34</v>
-      </c>
-      <c r="K60">
-        <f>$AQ$5</f>
-        <v>0.19</v>
-      </c>
-      <c r="L60" t="s">
-        <v>57</v>
-      </c>
-      <c r="M60">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="O60">
-        <f>$AN$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P60">
-        <f t="shared" si="25"/>
-        <v>7</v>
-      </c>
-      <c r="Q60">
-        <f t="shared" si="26"/>
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="R60">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="T60">
-        <f>$AQ$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U60">
-        <f>$AQ$4</f>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V60">
-        <f>$AN$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X60">
-        <f t="shared" si="21"/>
-        <v>0.78</v>
-      </c>
-      <c r="Y60">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="Z60">
-        <f>$AM$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA60">
-        <f t="shared" si="29"/>
-        <v>2.0597580800000003E-4</v>
-      </c>
-      <c r="AB60">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AC60">
-        <f t="shared" si="31"/>
-        <v>1.8043480780800005</v>
-      </c>
-      <c r="AD60">
-        <f t="shared" si="32"/>
+        <f>(AB59+AC59)*10^-3</f>
         <v>1.8043480780800005E-3</v>
       </c>
     </row>
